--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127020670</v>
+        <v>127020665</v>
       </c>
       <c r="B2" t="n">
-        <v>97245</v>
+        <v>80018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729978</v>
+        <v>730028</v>
       </c>
       <c r="R2" t="n">
-        <v>7217767</v>
+        <v>7217812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127020665</v>
+        <v>127020670</v>
       </c>
       <c r="B3" t="n">
-        <v>79987</v>
+        <v>97320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730028</v>
+        <v>729978</v>
       </c>
       <c r="R3" t="n">
-        <v>7217812</v>
+        <v>7217767</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020706</v>
+        <v>127020629</v>
       </c>
       <c r="B4" t="n">
         <v>57657</v>
@@ -902,7 +902,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729913</v>
+        <v>729893</v>
       </c>
       <c r="R4" t="n">
-        <v>7217887</v>
+        <v>7217893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +952,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127020629</v>
+        <v>127020706</v>
       </c>
       <c r="B5" t="n">
         <v>57657</v>
@@ -1012,7 +1012,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729893</v>
+        <v>729913</v>
       </c>
       <c r="R5" t="n">
-        <v>7217893</v>
+        <v>7217887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020704</v>
+        <v>127020692</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729985</v>
+        <v>729964</v>
       </c>
       <c r="R6" t="n">
-        <v>7217794</v>
+        <v>7217823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020692</v>
+        <v>127020704</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729964</v>
+        <v>729985</v>
       </c>
       <c r="R7" t="n">
-        <v>7217823</v>
+        <v>7217794</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127020662</v>
+        <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80112</v>
+        <v>80018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,21 +1294,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729959</v>
+        <v>729960</v>
       </c>
       <c r="R8" t="n">
-        <v>7217826</v>
+        <v>7217849</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127020664</v>
+        <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>79987</v>
+        <v>80143</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,21 +1391,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729960</v>
+        <v>729959</v>
       </c>
       <c r="R9" t="n">
-        <v>7217849</v>
+        <v>7217826</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020693</v>
+        <v>127020637</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729531</v>
+        <v>729482</v>
       </c>
       <c r="R10" t="n">
-        <v>7218052</v>
+        <v>7218068</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020688</v>
+        <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>91406</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729734</v>
+        <v>729531</v>
       </c>
       <c r="R11" t="n">
-        <v>7217951</v>
+        <v>7218052</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,32 +1671,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020637</v>
+        <v>127020688</v>
       </c>
       <c r="B12" t="n">
-        <v>79598</v>
+        <v>91480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729482</v>
+        <v>729734</v>
       </c>
       <c r="R12" t="n">
-        <v>7218068</v>
+        <v>7217951</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,7 +1881,7 @@
         <v>127020644</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>127020680</v>
       </c>
       <c r="B15" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,53 +2077,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020654</v>
+        <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729936</v>
+        <v>729961</v>
       </c>
       <c r="R16" t="n">
-        <v>7217870</v>
+        <v>7217852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2156,11 +2148,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2187,45 +2174,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020712</v>
+        <v>127020654</v>
       </c>
       <c r="B17" t="n">
-        <v>80118</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729961</v>
+        <v>729936</v>
       </c>
       <c r="R17" t="n">
-        <v>7217852</v>
+        <v>7217870</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2258,6 +2253,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,7 +2287,7 @@
         <v>127020702</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>92727</v>
+        <v>92802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>127020713</v>
       </c>
       <c r="B22" t="n">
-        <v>80118</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,53 +2770,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020631</v>
+        <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>80142</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729898</v>
+        <v>729977</v>
       </c>
       <c r="R23" t="n">
-        <v>7217887</v>
+        <v>7217779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,11 +2841,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2880,7 +2867,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020652</v>
+        <v>127020645</v>
       </c>
       <c r="B24" t="n">
         <v>57657</v>
@@ -2913,7 +2900,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2923,10 +2910,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729906</v>
+        <v>729635</v>
       </c>
       <c r="R24" t="n">
-        <v>7217885</v>
+        <v>7218021</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2963,7 +2950,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2990,7 +2977,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020645</v>
+        <v>127020631</v>
       </c>
       <c r="B25" t="n">
         <v>57657</v>
@@ -3023,7 +3010,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3033,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729635</v>
+        <v>729898</v>
       </c>
       <c r="R25" t="n">
-        <v>7218021</v>
+        <v>7217887</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3073,7 +3060,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack bild 2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3100,45 +3087,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020675</v>
+        <v>127020652</v>
       </c>
       <c r="B26" t="n">
-        <v>80111</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729977</v>
+        <v>729906</v>
       </c>
       <c r="R26" t="n">
-        <v>7217779</v>
+        <v>7217885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,6 +3166,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020679</v>
+        <v>127020639</v>
       </c>
       <c r="B27" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729853</v>
+        <v>729901</v>
       </c>
       <c r="R27" t="n">
-        <v>7217932</v>
+        <v>7217877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,7 +3276,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3298,7 +3297,7 @@
         <v>127020705</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3392,10 +3391,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020639</v>
+        <v>127020679</v>
       </c>
       <c r="B29" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3403,21 +3402,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3427,10 +3426,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>729901</v>
+        <v>729853</v>
       </c>
       <c r="R29" t="n">
-        <v>7217877</v>
+        <v>7217932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3471,6 +3470,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>127020666</v>
       </c>
       <c r="B30" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>75067</v>
+        <v>75127</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>127020635</v>
       </c>
       <c r="B33" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>127020694</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020646</v>
+        <v>127020700</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3994,42 +3994,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>731050</v>
+        <v>731060</v>
       </c>
       <c r="R35" t="n">
-        <v>7217071</v>
+        <v>7217069</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4062,11 +4054,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4096,7 +4083,7 @@
         <v>127020661</v>
       </c>
       <c r="B36" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4190,10 +4177,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020700</v>
+        <v>127020646</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4201,34 +4188,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>731060</v>
+        <v>731050</v>
       </c>
       <c r="R37" t="n">
-        <v>7217069</v>
+        <v>7217071</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4261,6 +4256,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4395,7 +4395,7 @@
         <v>127020711</v>
       </c>
       <c r="B39" t="n">
-        <v>80118</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>127020674</v>
       </c>
       <c r="B40" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020642</v>
+        <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>91245</v>
+        <v>57817</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730729</v>
+        <v>730778</v>
       </c>
       <c r="R42" t="n">
-        <v>7217314</v>
+        <v>7217220</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,6 +4791,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020655</v>
+        <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>57817</v>
+        <v>91319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4833,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730778</v>
+        <v>730729</v>
       </c>
       <c r="R43" t="n">
-        <v>7217220</v>
+        <v>7217314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,11 +4893,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5032,7 +5032,7 @@
         <v>127020691</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>127020699</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>127020701</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>127020697</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>127020689</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5519,32 +5519,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020710</v>
+        <v>127020632</v>
       </c>
       <c r="B50" t="n">
-        <v>80118</v>
+        <v>75135</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730874</v>
+        <v>730709</v>
       </c>
       <c r="R50" t="n">
-        <v>7217193</v>
+        <v>7217283</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5616,32 +5616,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020632</v>
+        <v>127020710</v>
       </c>
       <c r="B51" t="n">
-        <v>75075</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730709</v>
+        <v>730874</v>
       </c>
       <c r="R51" t="n">
-        <v>7217283</v>
+        <v>7217193</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5716,7 +5716,7 @@
         <v>127020669</v>
       </c>
       <c r="B52" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>127020695</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5912,10 +5912,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020696</v>
+        <v>127020690</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>730712</v>
       </c>
       <c r="R54" t="n">
-        <v>7217282</v>
+        <v>7217261</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5983,11 +5983,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6014,10 +6009,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020690</v>
+        <v>127020696</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6052,7 +6047,7 @@
         <v>730712</v>
       </c>
       <c r="R55" t="n">
-        <v>7217261</v>
+        <v>7217282</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6085,6 +6080,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6111,27 +6111,27 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020708</v>
+        <v>127020698</v>
       </c>
       <c r="B56" t="n">
-        <v>80118</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730721</v>
+        <v>730776</v>
       </c>
       <c r="R56" t="n">
-        <v>7217258</v>
+        <v>7217232</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6208,10 +6208,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020698</v>
+        <v>127020667</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>91615</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6219,21 +6219,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730776</v>
+        <v>730729</v>
       </c>
       <c r="R57" t="n">
-        <v>7217232</v>
+        <v>7217314</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,32 +6305,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020667</v>
+        <v>127020708</v>
       </c>
       <c r="B58" t="n">
-        <v>91541</v>
+        <v>80149</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730729</v>
+        <v>730721</v>
       </c>
       <c r="R58" t="n">
-        <v>7217314</v>
+        <v>7217258</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6405,7 +6405,7 @@
         <v>127020660</v>
       </c>
       <c r="B59" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020668</v>
+        <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>97245</v>
+        <v>80143</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>731110</v>
+        <v>730717</v>
       </c>
       <c r="R60" t="n">
-        <v>7217020</v>
+        <v>7217269</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020659</v>
+        <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>80112</v>
+        <v>97320</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,21 +6607,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730717</v>
+        <v>731110</v>
       </c>
       <c r="R61" t="n">
-        <v>7217269</v>
+        <v>7217020</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127020665</v>
+        <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>80018</v>
+        <v>97326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730028</v>
+        <v>729978</v>
       </c>
       <c r="R2" t="n">
-        <v>7217812</v>
+        <v>7217767</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127020670</v>
+        <v>127020665</v>
       </c>
       <c r="B3" t="n">
-        <v>97320</v>
+        <v>80021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729978</v>
+        <v>730028</v>
       </c>
       <c r="R3" t="n">
-        <v>7217767</v>
+        <v>7217812</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020692</v>
+        <v>127020704</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729964</v>
+        <v>729985</v>
       </c>
       <c r="R6" t="n">
-        <v>7217823</v>
+        <v>7217794</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020704</v>
+        <v>127020692</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729985</v>
+        <v>729964</v>
       </c>
       <c r="R7" t="n">
-        <v>7217794</v>
+        <v>7217823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1286,7 @@
         <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>127020637</v>
       </c>
       <c r="B10" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>127020688</v>
       </c>
       <c r="B12" t="n">
-        <v>91480</v>
+        <v>91486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020653</v>
+        <v>127020680</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,42 +1779,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729926</v>
+        <v>729872</v>
       </c>
       <c r="R13" t="n">
-        <v>7217876</v>
+        <v>7217916</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,17 +1841,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1881,7 +1869,7 @@
         <v>127020644</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,10 +1967,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020680</v>
+        <v>127020653</v>
       </c>
       <c r="B15" t="n">
-        <v>78770</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1990,34 +1978,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729872</v>
+        <v>729926</v>
       </c>
       <c r="R15" t="n">
-        <v>7217916</v>
+        <v>7217876</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,13 +2048,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2077,27 +2077,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020712</v>
+        <v>127020702</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729961</v>
+        <v>729956</v>
       </c>
       <c r="R16" t="n">
         <v>7217852</v>
@@ -2174,53 +2174,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020654</v>
+        <v>127020712</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>80152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729936</v>
+        <v>729961</v>
       </c>
       <c r="R17" t="n">
-        <v>7217870</v>
+        <v>7217852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2253,11 +2245,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2284,10 +2271,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020702</v>
+        <v>127020654</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2295,34 +2282,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729956</v>
+        <v>729936</v>
       </c>
       <c r="R18" t="n">
-        <v>7217852</v>
+        <v>7217870</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,6 +2350,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,7 +2384,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>92802</v>
+        <v>92808</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020671</v>
+        <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>58488</v>
+        <v>80152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,21 +2586,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208245</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730037</v>
+        <v>729972</v>
       </c>
       <c r="R21" t="n">
-        <v>7217806</v>
+        <v>7217816</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,7 +2654,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2673,10 +2672,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020713</v>
+        <v>127020671</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>58488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2684,21 +2683,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>208245</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2708,10 +2707,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729972</v>
+        <v>730037</v>
       </c>
       <c r="R22" t="n">
-        <v>7217816</v>
+        <v>7217806</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2752,6 +2751,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020639</v>
+        <v>127020705</v>
       </c>
       <c r="B27" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729901</v>
+        <v>729987</v>
       </c>
       <c r="R27" t="n">
-        <v>7217877</v>
+        <v>7217772</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020705</v>
+        <v>127020639</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3305,21 +3305,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729987</v>
+        <v>729901</v>
       </c>
       <c r="R28" t="n">
-        <v>7217772</v>
+        <v>7217877</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3394,7 +3394,7 @@
         <v>127020679</v>
       </c>
       <c r="B29" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>127020666</v>
       </c>
       <c r="B30" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>75127</v>
+        <v>75130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>127020635</v>
       </c>
       <c r="B33" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>127020694</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127020700</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>127020661</v>
       </c>
       <c r="B36" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>127020711</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>80152</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>127020674</v>
       </c>
       <c r="B40" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020655</v>
+        <v>127020642</v>
       </c>
       <c r="B42" t="n">
-        <v>57817</v>
+        <v>91325</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730778</v>
+        <v>730729</v>
       </c>
       <c r="R42" t="n">
-        <v>7217220</v>
+        <v>7217314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,11 +4791,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4822,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020642</v>
+        <v>127020655</v>
       </c>
       <c r="B43" t="n">
-        <v>91319</v>
+        <v>57817</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4857,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730729</v>
+        <v>730778</v>
       </c>
       <c r="R43" t="n">
-        <v>7217314</v>
+        <v>7217220</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,6 +4888,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5032,7 +5032,7 @@
         <v>127020691</v>
       </c>
       <c r="B45" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>127020699</v>
       </c>
       <c r="B46" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>127020701</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020697</v>
+        <v>127020689</v>
       </c>
       <c r="B48" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730722</v>
+        <v>730685</v>
       </c>
       <c r="R48" t="n">
-        <v>7217249</v>
+        <v>7217290</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5422,10 +5422,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127020689</v>
+        <v>127020697</v>
       </c>
       <c r="B49" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730685</v>
+        <v>730722</v>
       </c>
       <c r="R49" t="n">
-        <v>7217290</v>
+        <v>7217249</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5519,32 +5519,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020632</v>
+        <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>75135</v>
+        <v>80152</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730709</v>
+        <v>730874</v>
       </c>
       <c r="R50" t="n">
-        <v>7217283</v>
+        <v>7217193</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5616,32 +5616,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020710</v>
+        <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>75138</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730874</v>
+        <v>730709</v>
       </c>
       <c r="R51" t="n">
-        <v>7217193</v>
+        <v>7217283</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5716,7 +5716,7 @@
         <v>127020669</v>
       </c>
       <c r="B52" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>127020695</v>
       </c>
       <c r="B53" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>127020690</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>127020696</v>
       </c>
       <c r="B55" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>127020698</v>
       </c>
       <c r="B56" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6208,32 +6208,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020667</v>
+        <v>127020708</v>
       </c>
       <c r="B57" t="n">
-        <v>91615</v>
+        <v>80152</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730729</v>
+        <v>730721</v>
       </c>
       <c r="R57" t="n">
-        <v>7217314</v>
+        <v>7217258</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,32 +6305,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020708</v>
+        <v>127020667</v>
       </c>
       <c r="B58" t="n">
-        <v>80149</v>
+        <v>91621</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730721</v>
+        <v>730729</v>
       </c>
       <c r="R58" t="n">
-        <v>7217258</v>
+        <v>7217314</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6405,7 +6405,7 @@
         <v>127020660</v>
       </c>
       <c r="B59" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127020670</v>
+        <v>127020665</v>
       </c>
       <c r="B2" t="n">
-        <v>97326</v>
+        <v>80021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729978</v>
+        <v>730028</v>
       </c>
       <c r="R2" t="n">
-        <v>7217767</v>
+        <v>7217812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127020665</v>
+        <v>127020670</v>
       </c>
       <c r="B3" t="n">
-        <v>80021</v>
+        <v>97326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730028</v>
+        <v>729978</v>
       </c>
       <c r="R3" t="n">
-        <v>7217812</v>
+        <v>7217767</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020629</v>
+        <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729893</v>
+        <v>729985</v>
       </c>
       <c r="R4" t="n">
-        <v>7217893</v>
+        <v>7217794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127020706</v>
+        <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,42 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729913</v>
+        <v>729964</v>
       </c>
       <c r="R5" t="n">
-        <v>7217887</v>
+        <v>7217823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020704</v>
+        <v>127020629</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1074,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729985</v>
+        <v>729893</v>
       </c>
       <c r="R6" t="n">
-        <v>7217794</v>
+        <v>7217893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020692</v>
+        <v>127020706</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,34 +1184,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729964</v>
+        <v>729913</v>
       </c>
       <c r="R7" t="n">
-        <v>7217823</v>
+        <v>7217887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,6 +1252,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1574,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020693</v>
+        <v>127020688</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>91486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729531</v>
+        <v>729734</v>
       </c>
       <c r="R11" t="n">
-        <v>7218052</v>
+        <v>7217951</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,32 +1671,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020688</v>
+        <v>127020693</v>
       </c>
       <c r="B12" t="n">
-        <v>91486</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729734</v>
+        <v>729531</v>
       </c>
       <c r="R12" t="n">
-        <v>7217951</v>
+        <v>7218052</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2077,27 +2077,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020702</v>
+        <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729956</v>
+        <v>729961</v>
       </c>
       <c r="R16" t="n">
         <v>7217852</v>
@@ -2174,27 +2174,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020712</v>
+        <v>127020702</v>
       </c>
       <c r="B17" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729961</v>
+        <v>729956</v>
       </c>
       <c r="R17" t="n">
         <v>7217852</v>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020713</v>
+        <v>127020671</v>
       </c>
       <c r="B21" t="n">
-        <v>80152</v>
+        <v>58488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,21 +2586,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>208245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>729972</v>
+        <v>730037</v>
       </c>
       <c r="R21" t="n">
-        <v>7217816</v>
+        <v>7217806</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,6 +2654,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2673,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020671</v>
+        <v>127020713</v>
       </c>
       <c r="B22" t="n">
-        <v>58488</v>
+        <v>80152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2683,21 +2684,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2707,10 +2708,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730037</v>
+        <v>729972</v>
       </c>
       <c r="R22" t="n">
-        <v>7217806</v>
+        <v>7217816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2751,7 +2752,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020705</v>
+        <v>127020639</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729987</v>
+        <v>729901</v>
       </c>
       <c r="R27" t="n">
-        <v>7217772</v>
+        <v>7217877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020639</v>
+        <v>127020705</v>
       </c>
       <c r="B28" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3305,21 +3305,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729901</v>
+        <v>729987</v>
       </c>
       <c r="R28" t="n">
-        <v>7217877</v>
+        <v>7217772</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3983,32 +3983,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020700</v>
+        <v>127020661</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>731060</v>
+        <v>730715</v>
       </c>
       <c r="R35" t="n">
-        <v>7217069</v>
+        <v>7217263</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4080,45 +4080,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020661</v>
+        <v>127020646</v>
       </c>
       <c r="B36" t="n">
-        <v>80146</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730715</v>
+        <v>731050</v>
       </c>
       <c r="R36" t="n">
-        <v>7217263</v>
+        <v>7217071</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4151,6 +4159,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4177,10 +4190,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020646</v>
+        <v>127020700</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4188,42 +4201,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>731050</v>
+        <v>731060</v>
       </c>
       <c r="R37" t="n">
-        <v>7217071</v>
+        <v>7217069</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4256,11 +4261,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020642</v>
+        <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>91325</v>
+        <v>57817</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730729</v>
+        <v>730778</v>
       </c>
       <c r="R42" t="n">
-        <v>7217314</v>
+        <v>7217220</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,6 +4791,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020655</v>
+        <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>57817</v>
+        <v>91325</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4833,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730778</v>
+        <v>730729</v>
       </c>
       <c r="R43" t="n">
-        <v>7217220</v>
+        <v>7217314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,11 +4893,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5029,7 +5029,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127020691</v>
+        <v>127020701</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730593</v>
+        <v>730947</v>
       </c>
       <c r="R45" t="n">
-        <v>7217363</v>
+        <v>7217151</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5100,11 +5100,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>6st långa bålar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5228,7 +5223,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020701</v>
+        <v>127020691</v>
       </c>
       <c r="B47" t="n">
         <v>79014</v>
@@ -5263,10 +5258,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730947</v>
+        <v>730593</v>
       </c>
       <c r="R47" t="n">
-        <v>7217151</v>
+        <v>7217363</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5299,6 +5294,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>6st långa bålar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5325,7 +5325,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020689</v>
+        <v>127020697</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730685</v>
+        <v>730722</v>
       </c>
       <c r="R48" t="n">
-        <v>7217290</v>
+        <v>7217249</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127020697</v>
+        <v>127020689</v>
       </c>
       <c r="B49" t="n">
         <v>79014</v>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730722</v>
+        <v>730685</v>
       </c>
       <c r="R49" t="n">
-        <v>7217249</v>
+        <v>7217290</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5713,32 +5713,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020669</v>
+        <v>127020695</v>
       </c>
       <c r="B52" t="n">
-        <v>97326</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730976</v>
+        <v>730607</v>
       </c>
       <c r="R52" t="n">
-        <v>7217157</v>
+        <v>7217333</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5784,6 +5784,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5810,32 +5815,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020695</v>
+        <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>97326</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5845,10 +5850,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730607</v>
+        <v>730976</v>
       </c>
       <c r="R53" t="n">
-        <v>7217333</v>
+        <v>7217157</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5881,11 +5886,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6111,27 +6111,27 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020698</v>
+        <v>127020708</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730776</v>
+        <v>730721</v>
       </c>
       <c r="R56" t="n">
-        <v>7217232</v>
+        <v>7217258</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6208,32 +6208,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020708</v>
+        <v>127020667</v>
       </c>
       <c r="B57" t="n">
-        <v>80152</v>
+        <v>91621</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730721</v>
+        <v>730729</v>
       </c>
       <c r="R57" t="n">
-        <v>7217258</v>
+        <v>7217314</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,10 +6305,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020667</v>
+        <v>127020698</v>
       </c>
       <c r="B58" t="n">
-        <v>91621</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730729</v>
+        <v>730776</v>
       </c>
       <c r="R58" t="n">
-        <v>7217314</v>
+        <v>7217232</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -2770,45 +2770,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020675</v>
+        <v>127020645</v>
       </c>
       <c r="B23" t="n">
-        <v>80145</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729977</v>
+        <v>729635</v>
       </c>
       <c r="R23" t="n">
-        <v>7217779</v>
+        <v>7218021</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2841,6 +2849,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2867,7 +2880,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020645</v>
+        <v>127020631</v>
       </c>
       <c r="B24" t="n">
         <v>57657</v>
@@ -2900,7 +2913,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2910,10 +2923,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729635</v>
+        <v>729898</v>
       </c>
       <c r="R24" t="n">
-        <v>7218021</v>
+        <v>7217887</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,7 +2963,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack bild 2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2977,7 +2990,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020631</v>
+        <v>127020652</v>
       </c>
       <c r="B25" t="n">
         <v>57657</v>
@@ -3020,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729898</v>
+        <v>729906</v>
       </c>
       <c r="R25" t="n">
-        <v>7217887</v>
+        <v>7217885</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,53 +3100,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020652</v>
+        <v>127020675</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>80145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729906</v>
+        <v>729977</v>
       </c>
       <c r="R26" t="n">
-        <v>7217885</v>
+        <v>7217779</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3166,11 +3171,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5519,32 +5519,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020710</v>
+        <v>127020632</v>
       </c>
       <c r="B50" t="n">
-        <v>80152</v>
+        <v>75138</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730874</v>
+        <v>730709</v>
       </c>
       <c r="R50" t="n">
-        <v>7217193</v>
+        <v>7217283</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5616,32 +5616,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020632</v>
+        <v>127020710</v>
       </c>
       <c r="B51" t="n">
-        <v>75138</v>
+        <v>80152</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730709</v>
+        <v>730874</v>
       </c>
       <c r="R51" t="n">
-        <v>7217283</v>
+        <v>7217193</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127020670</v>
       </c>
       <c r="B3" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1477,32 +1477,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020637</v>
+        <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>79632</v>
+        <v>91487</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729482</v>
+        <v>729734</v>
       </c>
       <c r="R10" t="n">
-        <v>7218068</v>
+        <v>7217951</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020688</v>
+        <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>91486</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729734</v>
+        <v>729531</v>
       </c>
       <c r="R11" t="n">
-        <v>7217951</v>
+        <v>7218052</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020693</v>
+        <v>127020637</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1682,21 +1682,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729531</v>
+        <v>729482</v>
       </c>
       <c r="R12" t="n">
-        <v>7218052</v>
+        <v>7218068</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2077,27 +2077,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020712</v>
+        <v>127020702</v>
       </c>
       <c r="B16" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729961</v>
+        <v>729956</v>
       </c>
       <c r="R16" t="n">
         <v>7217852</v>
@@ -2174,27 +2174,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020702</v>
+        <v>127020712</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729956</v>
+        <v>729961</v>
       </c>
       <c r="R17" t="n">
         <v>7217852</v>
@@ -2384,7 +2384,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020671</v>
+        <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>58488</v>
+        <v>80152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,21 +2586,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208245</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730037</v>
+        <v>729972</v>
       </c>
       <c r="R21" t="n">
-        <v>7217806</v>
+        <v>7217816</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,7 +2654,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2673,10 +2672,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020713</v>
+        <v>127020671</v>
       </c>
       <c r="B22" t="n">
-        <v>80152</v>
+        <v>58488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2684,21 +2683,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>208245</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2708,10 +2707,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729972</v>
+        <v>730037</v>
       </c>
       <c r="R22" t="n">
-        <v>7217816</v>
+        <v>7217806</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2752,6 +2751,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2770,53 +2770,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020645</v>
+        <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>80145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729635</v>
+        <v>729977</v>
       </c>
       <c r="R23" t="n">
-        <v>7218021</v>
+        <v>7217779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,11 +2841,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2880,7 +2867,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020631</v>
+        <v>127020645</v>
       </c>
       <c r="B24" t="n">
         <v>57657</v>
@@ -2913,7 +2900,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2923,10 +2910,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729898</v>
+        <v>729635</v>
       </c>
       <c r="R24" t="n">
-        <v>7217887</v>
+        <v>7218021</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2963,7 +2950,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2990,7 +2977,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020652</v>
+        <v>127020631</v>
       </c>
       <c r="B25" t="n">
         <v>57657</v>
@@ -3033,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729906</v>
+        <v>729898</v>
       </c>
       <c r="R25" t="n">
-        <v>7217885</v>
+        <v>7217887</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3100,45 +3087,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020675</v>
+        <v>127020652</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729977</v>
+        <v>729906</v>
       </c>
       <c r="R26" t="n">
-        <v>7217779</v>
+        <v>7217885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,6 +3166,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020639</v>
+        <v>127020679</v>
       </c>
       <c r="B27" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729901</v>
+        <v>729853</v>
       </c>
       <c r="R27" t="n">
-        <v>7217877</v>
+        <v>7217932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,6 +3276,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3391,10 +3392,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020679</v>
+        <v>127020639</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3402,21 +3403,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3426,10 +3427,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>729853</v>
+        <v>729901</v>
       </c>
       <c r="R29" t="n">
-        <v>7217932</v>
+        <v>7217877</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,7 +3471,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4080,10 +4080,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020646</v>
+        <v>127020700</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4091,42 +4091,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731050</v>
+        <v>731060</v>
       </c>
       <c r="R36" t="n">
-        <v>7217071</v>
+        <v>7217069</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4159,11 +4151,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4190,10 +4177,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020700</v>
+        <v>127020646</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4201,34 +4188,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>731060</v>
+        <v>731050</v>
       </c>
       <c r="R37" t="n">
-        <v>7217069</v>
+        <v>7217071</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4261,6 +4256,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020655</v>
+        <v>127020642</v>
       </c>
       <c r="B42" t="n">
-        <v>57817</v>
+        <v>91326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730778</v>
+        <v>730729</v>
       </c>
       <c r="R42" t="n">
-        <v>7217220</v>
+        <v>7217314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,11 +4791,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4822,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020642</v>
+        <v>127020655</v>
       </c>
       <c r="B43" t="n">
-        <v>91325</v>
+        <v>57817</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4857,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730729</v>
+        <v>730778</v>
       </c>
       <c r="R43" t="n">
-        <v>7217314</v>
+        <v>7217220</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,6 +4888,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5029,7 +5029,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127020701</v>
+        <v>127020691</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730947</v>
+        <v>730593</v>
       </c>
       <c r="R45" t="n">
-        <v>7217151</v>
+        <v>7217363</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5100,6 +5100,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>6st långa bålar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5223,7 +5228,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020691</v>
+        <v>127020701</v>
       </c>
       <c r="B47" t="n">
         <v>79014</v>
@@ -5258,10 +5263,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730593</v>
+        <v>730947</v>
       </c>
       <c r="R47" t="n">
-        <v>7217363</v>
+        <v>7217151</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5294,11 +5299,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>6st långa bålar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5818,7 +5818,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6111,32 +6111,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020708</v>
+        <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>80152</v>
+        <v>91622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730721</v>
+        <v>730729</v>
       </c>
       <c r="R56" t="n">
-        <v>7217258</v>
+        <v>7217314</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6208,10 +6208,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020667</v>
+        <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>91621</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6219,21 +6219,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730729</v>
+        <v>730776</v>
       </c>
       <c r="R57" t="n">
-        <v>7217314</v>
+        <v>7217232</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,27 +6305,27 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020698</v>
+        <v>127020708</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730776</v>
+        <v>730721</v>
       </c>
       <c r="R58" t="n">
-        <v>7217232</v>
+        <v>7217258</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6599,7 +6599,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020680</v>
+        <v>127020644</v>
       </c>
       <c r="B13" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,34 +1779,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729872</v>
+        <v>729994</v>
       </c>
       <c r="R13" t="n">
-        <v>7217916</v>
+        <v>7217784</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020644</v>
+        <v>127020653</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1877,26 +1880,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1904,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729994</v>
+        <v>729926</v>
       </c>
       <c r="R14" t="n">
-        <v>7217784</v>
+        <v>7217876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1942,13 +1950,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1967,10 +1979,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020653</v>
+        <v>127020680</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,42 +1990,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729926</v>
+        <v>729872</v>
       </c>
       <c r="R15" t="n">
-        <v>7217876</v>
+        <v>7217916</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,17 +2052,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020713</v>
+        <v>127020671</v>
       </c>
       <c r="B21" t="n">
-        <v>80152</v>
+        <v>58488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,21 +2586,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>208245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>729972</v>
+        <v>730037</v>
       </c>
       <c r="R21" t="n">
-        <v>7217816</v>
+        <v>7217806</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,6 +2654,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2673,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020671</v>
+        <v>127020713</v>
       </c>
       <c r="B22" t="n">
-        <v>58488</v>
+        <v>80152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2683,21 +2684,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2707,10 +2708,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730037</v>
+        <v>729972</v>
       </c>
       <c r="R22" t="n">
-        <v>7217806</v>
+        <v>7217816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2751,7 +2752,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -4513,45 +4513,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020674</v>
+        <v>127020648</v>
       </c>
       <c r="B40" t="n">
-        <v>80145</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>731014</v>
+        <v>730971</v>
       </c>
       <c r="R40" t="n">
-        <v>7217177</v>
+        <v>7217152</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4584,6 +4592,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4610,53 +4623,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020648</v>
+        <v>127020674</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>80145</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730971</v>
+        <v>731014</v>
       </c>
       <c r="R41" t="n">
-        <v>7217152</v>
+        <v>7217177</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,11 +4694,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020704</v>
+        <v>127020629</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729985</v>
+        <v>729893</v>
       </c>
       <c r="R4" t="n">
-        <v>7217794</v>
+        <v>7217893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127020692</v>
+        <v>127020706</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +990,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729964</v>
+        <v>729913</v>
       </c>
       <c r="R5" t="n">
-        <v>7217823</v>
+        <v>7217887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020629</v>
+        <v>127020704</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,42 +1100,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729893</v>
+        <v>729985</v>
       </c>
       <c r="R6" t="n">
-        <v>7217893</v>
+        <v>7217794</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,11 +1160,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020706</v>
+        <v>127020692</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,42 +1197,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729913</v>
+        <v>729964</v>
       </c>
       <c r="R7" t="n">
-        <v>7217887</v>
+        <v>7217823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,11 +1257,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1477,32 +1477,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020688</v>
+        <v>127020693</v>
       </c>
       <c r="B10" t="n">
-        <v>91487</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729734</v>
+        <v>729531</v>
       </c>
       <c r="R10" t="n">
-        <v>7217951</v>
+        <v>7218052</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020693</v>
+        <v>127020688</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>91487</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729531</v>
+        <v>729734</v>
       </c>
       <c r="R11" t="n">
-        <v>7218052</v>
+        <v>7217951</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020644</v>
+        <v>127020653</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,26 +1779,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1806,10 +1811,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729994</v>
+        <v>729926</v>
       </c>
       <c r="R13" t="n">
-        <v>7217784</v>
+        <v>7217876</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,13 +1849,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1869,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020653</v>
+        <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,42 +1889,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729926</v>
+        <v>729872</v>
       </c>
       <c r="R14" t="n">
-        <v>7217876</v>
+        <v>7217916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,17 +1951,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1979,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020680</v>
+        <v>127020644</v>
       </c>
       <c r="B15" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1990,34 +1987,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729872</v>
+        <v>729994</v>
       </c>
       <c r="R15" t="n">
-        <v>7217916</v>
+        <v>7217784</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2770,45 +2770,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020675</v>
+        <v>127020645</v>
       </c>
       <c r="B23" t="n">
-        <v>80145</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729977</v>
+        <v>729635</v>
       </c>
       <c r="R23" t="n">
-        <v>7217779</v>
+        <v>7218021</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2841,6 +2849,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2867,7 +2880,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020645</v>
+        <v>127020631</v>
       </c>
       <c r="B24" t="n">
         <v>57657</v>
@@ -2900,7 +2913,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2910,10 +2923,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729635</v>
+        <v>729898</v>
       </c>
       <c r="R24" t="n">
-        <v>7218021</v>
+        <v>7217887</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,7 +2963,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack bild 2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2977,7 +2990,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020631</v>
+        <v>127020652</v>
       </c>
       <c r="B25" t="n">
         <v>57657</v>
@@ -3020,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729898</v>
+        <v>729906</v>
       </c>
       <c r="R25" t="n">
-        <v>7217887</v>
+        <v>7217885</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,53 +3100,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020652</v>
+        <v>127020675</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>80145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729906</v>
+        <v>729977</v>
       </c>
       <c r="R26" t="n">
-        <v>7217885</v>
+        <v>7217779</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3166,11 +3171,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020679</v>
+        <v>127020705</v>
       </c>
       <c r="B27" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729853</v>
+        <v>729987</v>
       </c>
       <c r="R27" t="n">
-        <v>7217932</v>
+        <v>7217772</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,7 +3276,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3295,10 +3294,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020705</v>
+        <v>127020639</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3306,21 +3305,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3330,10 +3329,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729987</v>
+        <v>729901</v>
       </c>
       <c r="R28" t="n">
-        <v>7217772</v>
+        <v>7217877</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,10 +3391,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020639</v>
+        <v>127020679</v>
       </c>
       <c r="B29" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3403,21 +3402,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3427,10 +3426,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>729901</v>
+        <v>729853</v>
       </c>
       <c r="R29" t="n">
-        <v>7217877</v>
+        <v>7217932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3471,6 +3470,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4287,42 +4287,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020663</v>
+        <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>57654</v>
+        <v>80152</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4330,10 +4325,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730859</v>
+        <v>730711</v>
       </c>
       <c r="R38" t="n">
-        <v>7217175</v>
+        <v>7217270</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4368,14 +4363,35 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran, hoppat över från sälg som stod mycket nära</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4392,37 +4408,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127020711</v>
+        <v>127020663</v>
       </c>
       <c r="B39" t="n">
-        <v>80152</v>
+        <v>57654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4430,10 +4451,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730711</v>
+        <v>730859</v>
       </c>
       <c r="R39" t="n">
-        <v>7217270</v>
+        <v>7217175</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4468,35 +4489,14 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gran, hoppat över från sälg som stod mycket nära</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4513,53 +4513,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020648</v>
+        <v>127020674</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>80145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730971</v>
+        <v>731014</v>
       </c>
       <c r="R40" t="n">
-        <v>7217152</v>
+        <v>7217177</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4592,11 +4584,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4623,45 +4610,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020674</v>
+        <v>127020648</v>
       </c>
       <c r="B41" t="n">
-        <v>80145</v>
+        <v>57657</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>731014</v>
+        <v>730971</v>
       </c>
       <c r="R41" t="n">
-        <v>7217177</v>
+        <v>7217152</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4694,6 +4689,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020642</v>
+        <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>91326</v>
+        <v>57817</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730729</v>
+        <v>730778</v>
       </c>
       <c r="R42" t="n">
-        <v>7217314</v>
+        <v>7217220</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,6 +4791,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020655</v>
+        <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>57817</v>
+        <v>91326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4833,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730778</v>
+        <v>730729</v>
       </c>
       <c r="R43" t="n">
-        <v>7217220</v>
+        <v>7217314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,11 +4893,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5519,32 +5519,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020632</v>
+        <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>75138</v>
+        <v>80152</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730709</v>
+        <v>730874</v>
       </c>
       <c r="R50" t="n">
-        <v>7217283</v>
+        <v>7217193</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5616,32 +5616,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020710</v>
+        <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>80152</v>
+        <v>75138</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730874</v>
+        <v>730709</v>
       </c>
       <c r="R51" t="n">
-        <v>7217193</v>
+        <v>7217283</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6111,32 +6111,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020667</v>
+        <v>127020708</v>
       </c>
       <c r="B56" t="n">
-        <v>91622</v>
+        <v>80152</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730729</v>
+        <v>730721</v>
       </c>
       <c r="R56" t="n">
-        <v>7217314</v>
+        <v>7217258</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6305,32 +6305,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020708</v>
+        <v>127020667</v>
       </c>
       <c r="B58" t="n">
-        <v>80152</v>
+        <v>91622</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730721</v>
+        <v>730729</v>
       </c>
       <c r="R58" t="n">
-        <v>7217258</v>
+        <v>7217314</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020659</v>
+        <v>127020668</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>97327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730717</v>
+        <v>731110</v>
       </c>
       <c r="R60" t="n">
-        <v>7217269</v>
+        <v>7217020</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020668</v>
+        <v>127020659</v>
       </c>
       <c r="B61" t="n">
-        <v>97327</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,21 +6607,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>731110</v>
+        <v>730717</v>
       </c>
       <c r="R61" t="n">
-        <v>7217020</v>
+        <v>7217269</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -2174,45 +2174,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020712</v>
+        <v>127020654</v>
       </c>
       <c r="B17" t="n">
-        <v>80152</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729961</v>
+        <v>729936</v>
       </c>
       <c r="R17" t="n">
-        <v>7217852</v>
+        <v>7217870</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2245,6 +2253,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2271,53 +2284,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020654</v>
+        <v>127020712</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>80152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729936</v>
+        <v>729961</v>
       </c>
       <c r="R18" t="n">
-        <v>7217870</v>
+        <v>7217852</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2350,11 +2355,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020655</v>
+        <v>127020642</v>
       </c>
       <c r="B42" t="n">
-        <v>57817</v>
+        <v>91326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730778</v>
+        <v>730729</v>
       </c>
       <c r="R42" t="n">
-        <v>7217220</v>
+        <v>7217314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,11 +4791,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4822,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020642</v>
+        <v>127020655</v>
       </c>
       <c r="B43" t="n">
-        <v>91326</v>
+        <v>57817</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4857,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730729</v>
+        <v>730778</v>
       </c>
       <c r="R43" t="n">
-        <v>7217314</v>
+        <v>7217220</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,6 +4888,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -1574,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020688</v>
+        <v>127020637</v>
       </c>
       <c r="B11" t="n">
-        <v>91487</v>
+        <v>79632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729734</v>
+        <v>729482</v>
       </c>
       <c r="R11" t="n">
-        <v>7217951</v>
+        <v>7218068</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,32 +1671,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020637</v>
+        <v>127020688</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>91487</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729482</v>
+        <v>729734</v>
       </c>
       <c r="R12" t="n">
-        <v>7218068</v>
+        <v>7217951</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020653</v>
+        <v>127020644</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,31 +1779,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1811,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729926</v>
+        <v>729994</v>
       </c>
       <c r="R13" t="n">
-        <v>7217876</v>
+        <v>7217784</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,17 +1844,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1976,10 +1967,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020644</v>
+        <v>127020653</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,26 +1978,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2014,10 +2010,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729994</v>
+        <v>729926</v>
       </c>
       <c r="R15" t="n">
-        <v>7217784</v>
+        <v>7217876</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,13 +2048,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2174,53 +2174,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020654</v>
+        <v>127020712</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>80152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729936</v>
+        <v>729961</v>
       </c>
       <c r="R17" t="n">
-        <v>7217870</v>
+        <v>7217852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2253,11 +2245,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2284,45 +2271,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020712</v>
+        <v>127020654</v>
       </c>
       <c r="B18" t="n">
-        <v>80152</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729961</v>
+        <v>729936</v>
       </c>
       <c r="R18" t="n">
-        <v>7217852</v>
+        <v>7217870</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,6 +2350,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020642</v>
+        <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>91326</v>
+        <v>57817</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730729</v>
+        <v>730778</v>
       </c>
       <c r="R42" t="n">
-        <v>7217314</v>
+        <v>7217220</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,6 +4791,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020655</v>
+        <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>57817</v>
+        <v>91326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4833,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730778</v>
+        <v>730729</v>
       </c>
       <c r="R43" t="n">
-        <v>7217220</v>
+        <v>7217314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,11 +4893,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5713,32 +5713,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020695</v>
+        <v>127020669</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730607</v>
+        <v>730976</v>
       </c>
       <c r="R52" t="n">
-        <v>7217333</v>
+        <v>7217157</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5784,11 +5784,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5815,32 +5810,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020669</v>
+        <v>127020695</v>
       </c>
       <c r="B53" t="n">
-        <v>97327</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5850,10 +5845,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730976</v>
+        <v>730607</v>
       </c>
       <c r="R53" t="n">
-        <v>7217157</v>
+        <v>7217333</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5886,6 +5881,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127020665</v>
+        <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>80021</v>
+        <v>97331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730028</v>
+        <v>729978</v>
       </c>
       <c r="R2" t="n">
-        <v>7217812</v>
+        <v>7217767</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127020670</v>
+        <v>127020665</v>
       </c>
       <c r="B3" t="n">
-        <v>97327</v>
+        <v>80025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729978</v>
+        <v>730028</v>
       </c>
       <c r="R3" t="n">
-        <v>7217767</v>
+        <v>7217812</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020629</v>
+        <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729893</v>
+        <v>729985</v>
       </c>
       <c r="R4" t="n">
-        <v>7217893</v>
+        <v>7217794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127020706</v>
+        <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,42 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729913</v>
+        <v>729964</v>
       </c>
       <c r="R5" t="n">
-        <v>7217887</v>
+        <v>7217823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020704</v>
+        <v>127020629</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1074,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729985</v>
+        <v>729893</v>
       </c>
       <c r="R6" t="n">
-        <v>7217794</v>
+        <v>7217893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020692</v>
+        <v>127020706</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,34 +1184,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729964</v>
+        <v>729913</v>
       </c>
       <c r="R7" t="n">
-        <v>7217823</v>
+        <v>7217887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,6 +1252,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127020664</v>
+        <v>127020662</v>
       </c>
       <c r="B8" t="n">
-        <v>80021</v>
+        <v>80150</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,21 +1294,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729960</v>
+        <v>729959</v>
       </c>
       <c r="R8" t="n">
-        <v>7217849</v>
+        <v>7217826</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127020662</v>
+        <v>127020664</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>80025</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,21 +1391,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729959</v>
+        <v>729960</v>
       </c>
       <c r="R9" t="n">
-        <v>7217826</v>
+        <v>7217849</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,32 +1477,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020693</v>
+        <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>91491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729531</v>
+        <v>729734</v>
       </c>
       <c r="R10" t="n">
-        <v>7218052</v>
+        <v>7217951</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,7 +1577,7 @@
         <v>127020637</v>
       </c>
       <c r="B11" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,32 +1671,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020688</v>
+        <v>127020693</v>
       </c>
       <c r="B12" t="n">
-        <v>91487</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729734</v>
+        <v>729531</v>
       </c>
       <c r="R12" t="n">
-        <v>7217951</v>
+        <v>7218052</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
         <v>127020644</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>127020653</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,27 +2077,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020702</v>
+        <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>80156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729956</v>
+        <v>729961</v>
       </c>
       <c r="R16" t="n">
         <v>7217852</v>
@@ -2174,27 +2174,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020712</v>
+        <v>127020702</v>
       </c>
       <c r="B17" t="n">
-        <v>80152</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729961</v>
+        <v>729956</v>
       </c>
       <c r="R17" t="n">
         <v>7217852</v>
@@ -2274,7 +2274,7 @@
         <v>127020654</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020671</v>
+        <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>58488</v>
+        <v>80156</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,21 +2586,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208245</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730037</v>
+        <v>729972</v>
       </c>
       <c r="R21" t="n">
-        <v>7217806</v>
+        <v>7217816</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,7 +2654,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2673,10 +2672,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020713</v>
+        <v>127020671</v>
       </c>
       <c r="B22" t="n">
-        <v>80152</v>
+        <v>58492</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2684,21 +2683,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>208245</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2708,10 +2707,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729972</v>
+        <v>730037</v>
       </c>
       <c r="R22" t="n">
-        <v>7217816</v>
+        <v>7217806</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2752,6 +2751,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2770,53 +2770,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020645</v>
+        <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729635</v>
+        <v>729977</v>
       </c>
       <c r="R23" t="n">
-        <v>7218021</v>
+        <v>7217779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,11 +2841,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2880,10 +2867,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020631</v>
+        <v>127020645</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2913,7 +2900,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2923,10 +2910,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729898</v>
+        <v>729635</v>
       </c>
       <c r="R24" t="n">
-        <v>7217887</v>
+        <v>7218021</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2963,7 +2950,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2990,10 +2977,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020652</v>
+        <v>127020631</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729906</v>
+        <v>729898</v>
       </c>
       <c r="R25" t="n">
-        <v>7217885</v>
+        <v>7217887</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3100,45 +3087,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020675</v>
+        <v>127020652</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729977</v>
+        <v>729906</v>
       </c>
       <c r="R26" t="n">
-        <v>7217779</v>
+        <v>7217885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,6 +3166,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020705</v>
+        <v>127020639</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729987</v>
+        <v>729901</v>
       </c>
       <c r="R27" t="n">
-        <v>7217772</v>
+        <v>7217877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020639</v>
+        <v>127020705</v>
       </c>
       <c r="B28" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3305,21 +3305,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729901</v>
+        <v>729987</v>
       </c>
       <c r="R28" t="n">
-        <v>7217877</v>
+        <v>7217772</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3394,7 +3394,7 @@
         <v>127020679</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>127020666</v>
       </c>
       <c r="B30" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>75130</v>
+        <v>75134</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>127020658</v>
       </c>
       <c r="B32" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>127020635</v>
       </c>
       <c r="B33" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>127020694</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127020661</v>
       </c>
       <c r="B35" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>127020700</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>127020646</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>80152</v>
+        <v>80156</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>127020663</v>
       </c>
       <c r="B39" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>127020674</v>
       </c>
       <c r="B40" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>127020648</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>127020647</v>
       </c>
       <c r="B44" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>127020691</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>127020699</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>127020701</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>127020697</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>127020689</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>80152</v>
+        <v>80156</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,32 +5713,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020669</v>
+        <v>127020695</v>
       </c>
       <c r="B52" t="n">
-        <v>97327</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730976</v>
+        <v>730607</v>
       </c>
       <c r="R52" t="n">
-        <v>7217157</v>
+        <v>7217333</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5784,6 +5784,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5810,32 +5815,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020695</v>
+        <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>97331</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5845,10 +5850,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730607</v>
+        <v>730976</v>
       </c>
       <c r="R53" t="n">
-        <v>7217333</v>
+        <v>7217157</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5881,11 +5886,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5912,10 +5912,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020690</v>
+        <v>127020696</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>730712</v>
       </c>
       <c r="R54" t="n">
-        <v>7217261</v>
+        <v>7217282</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5983,6 +5983,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6009,10 +6014,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020696</v>
+        <v>127020690</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6047,7 +6052,7 @@
         <v>730712</v>
       </c>
       <c r="R55" t="n">
-        <v>7217282</v>
+        <v>7217261</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6080,11 +6085,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6114,7 +6114,7 @@
         <v>127020708</v>
       </c>
       <c r="B56" t="n">
-        <v>80152</v>
+        <v>80156</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6208,10 +6208,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020698</v>
+        <v>127020667</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>91626</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6219,21 +6219,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730776</v>
+        <v>730729</v>
       </c>
       <c r="R57" t="n">
-        <v>7217232</v>
+        <v>7217314</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,10 +6305,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020667</v>
+        <v>127020698</v>
       </c>
       <c r="B58" t="n">
-        <v>91622</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730729</v>
+        <v>730776</v>
       </c>
       <c r="R58" t="n">
-        <v>7217314</v>
+        <v>7217232</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6405,7 +6405,7 @@
         <v>127020660</v>
       </c>
       <c r="B59" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020668</v>
+        <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>97327</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>731110</v>
+        <v>730717</v>
       </c>
       <c r="R60" t="n">
-        <v>7217020</v>
+        <v>7217269</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020659</v>
+        <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>97331</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,21 +6607,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730717</v>
+        <v>731110</v>
       </c>
       <c r="R61" t="n">
-        <v>7217269</v>
+        <v>7217020</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127020670</v>
+        <v>127020665</v>
       </c>
       <c r="B2" t="n">
-        <v>97331</v>
+        <v>80025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729978</v>
+        <v>730028</v>
       </c>
       <c r="R2" t="n">
-        <v>7217767</v>
+        <v>7217812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127020665</v>
+        <v>127020670</v>
       </c>
       <c r="B3" t="n">
-        <v>80025</v>
+        <v>97331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730028</v>
+        <v>729978</v>
       </c>
       <c r="R3" t="n">
-        <v>7217812</v>
+        <v>7217767</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020704</v>
+        <v>127020629</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729985</v>
+        <v>729893</v>
       </c>
       <c r="R4" t="n">
-        <v>7217794</v>
+        <v>7217893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127020692</v>
+        <v>127020706</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +990,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729964</v>
+        <v>729913</v>
       </c>
       <c r="R5" t="n">
-        <v>7217823</v>
+        <v>7217887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020629</v>
+        <v>127020692</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,42 +1100,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729893</v>
+        <v>729964</v>
       </c>
       <c r="R6" t="n">
-        <v>7217893</v>
+        <v>7217823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,11 +1160,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020706</v>
+        <v>127020704</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,42 +1197,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729913</v>
+        <v>729985</v>
       </c>
       <c r="R7" t="n">
-        <v>7217887</v>
+        <v>7217794</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,11 +1257,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127020662</v>
+        <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80150</v>
+        <v>80025</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,21 +1294,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729959</v>
+        <v>729960</v>
       </c>
       <c r="R8" t="n">
-        <v>7217826</v>
+        <v>7217849</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127020664</v>
+        <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>80025</v>
+        <v>80150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,21 +1391,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729960</v>
+        <v>729959</v>
       </c>
       <c r="R9" t="n">
-        <v>7217849</v>
+        <v>7217826</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,32 +1477,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020688</v>
+        <v>127020637</v>
       </c>
       <c r="B10" t="n">
-        <v>91491</v>
+        <v>79636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729734</v>
+        <v>729482</v>
       </c>
       <c r="R10" t="n">
-        <v>7217951</v>
+        <v>7218068</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020637</v>
+        <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729482</v>
+        <v>729531</v>
       </c>
       <c r="R11" t="n">
-        <v>7218068</v>
+        <v>7218052</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,32 +1671,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020693</v>
+        <v>127020688</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>91491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729531</v>
+        <v>729734</v>
       </c>
       <c r="R12" t="n">
-        <v>7218052</v>
+        <v>7217951</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020713</v>
+        <v>127020671</v>
       </c>
       <c r="B21" t="n">
-        <v>80156</v>
+        <v>58492</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,21 +2586,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>208245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>729972</v>
+        <v>730037</v>
       </c>
       <c r="R21" t="n">
-        <v>7217816</v>
+        <v>7217806</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,6 +2654,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2673,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020671</v>
+        <v>127020713</v>
       </c>
       <c r="B22" t="n">
-        <v>58492</v>
+        <v>80156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2683,21 +2684,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2707,10 +2708,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730037</v>
+        <v>729972</v>
       </c>
       <c r="R22" t="n">
-        <v>7217806</v>
+        <v>7217816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2751,7 +2752,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2867,7 +2867,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020645</v>
+        <v>127020652</v>
       </c>
       <c r="B24" t="n">
         <v>57661</v>
@@ -2900,7 +2900,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729635</v>
+        <v>729906</v>
       </c>
       <c r="R24" t="n">
-        <v>7218021</v>
+        <v>7217885</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack bild 2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2977,7 +2977,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020631</v>
+        <v>127020645</v>
       </c>
       <c r="B25" t="n">
         <v>57661</v>
@@ -3010,7 +3010,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729898</v>
+        <v>729635</v>
       </c>
       <c r="R25" t="n">
-        <v>7217887</v>
+        <v>7218021</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3087,7 +3087,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020652</v>
+        <v>127020631</v>
       </c>
       <c r="B26" t="n">
         <v>57661</v>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729906</v>
+        <v>729898</v>
       </c>
       <c r="R26" t="n">
-        <v>7217885</v>
+        <v>7217887</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4287,37 +4287,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020711</v>
+        <v>127020663</v>
       </c>
       <c r="B38" t="n">
-        <v>80156</v>
+        <v>57658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4325,10 +4330,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730711</v>
+        <v>730859</v>
       </c>
       <c r="R38" t="n">
-        <v>7217270</v>
+        <v>7217175</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4363,35 +4368,14 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran, hoppat över från sälg som stod mycket nära</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4408,42 +4392,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127020663</v>
+        <v>127020711</v>
       </c>
       <c r="B39" t="n">
-        <v>57658</v>
+        <v>80156</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4451,10 +4430,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730859</v>
+        <v>730711</v>
       </c>
       <c r="R39" t="n">
-        <v>7217175</v>
+        <v>7217270</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4489,14 +4468,35 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gran, hoppat över från sälg som stod mycket nära</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5912,7 +5912,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020696</v>
+        <v>127020690</v>
       </c>
       <c r="B54" t="n">
         <v>79018</v>
@@ -5950,7 +5950,7 @@
         <v>730712</v>
       </c>
       <c r="R54" t="n">
-        <v>7217282</v>
+        <v>7217261</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5983,11 +5983,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6014,7 +6009,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020690</v>
+        <v>127020696</v>
       </c>
       <c r="B55" t="n">
         <v>79018</v>
@@ -6052,7 +6047,7 @@
         <v>730712</v>
       </c>
       <c r="R55" t="n">
-        <v>7217261</v>
+        <v>7217282</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6085,6 +6080,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6208,10 +6208,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020667</v>
+        <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>91626</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6219,21 +6219,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730729</v>
+        <v>730776</v>
       </c>
       <c r="R57" t="n">
-        <v>7217314</v>
+        <v>7217232</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,10 +6305,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020698</v>
+        <v>127020667</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>91626</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730776</v>
+        <v>730729</v>
       </c>
       <c r="R58" t="n">
-        <v>7217232</v>
+        <v>7217314</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020659</v>
+        <v>127020668</v>
       </c>
       <c r="B60" t="n">
-        <v>80150</v>
+        <v>97331</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730717</v>
+        <v>731110</v>
       </c>
       <c r="R60" t="n">
-        <v>7217269</v>
+        <v>7217020</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020668</v>
+        <v>127020659</v>
       </c>
       <c r="B61" t="n">
-        <v>97331</v>
+        <v>80150</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,21 +6607,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>731110</v>
+        <v>730717</v>
       </c>
       <c r="R61" t="n">
-        <v>7217020</v>
+        <v>7217269</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -1089,7 +1089,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020692</v>
+        <v>127020704</v>
       </c>
       <c r="B6" t="n">
         <v>79018</v>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729964</v>
+        <v>729985</v>
       </c>
       <c r="R6" t="n">
-        <v>7217823</v>
+        <v>7217794</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020704</v>
+        <v>127020692</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729985</v>
+        <v>729964</v>
       </c>
       <c r="R7" t="n">
-        <v>7217794</v>
+        <v>7217823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020680</v>
+        <v>127020653</v>
       </c>
       <c r="B14" t="n">
-        <v>78777</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1880,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729872</v>
+        <v>729926</v>
       </c>
       <c r="R14" t="n">
-        <v>7217916</v>
+        <v>7217876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1942,13 +1950,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1967,10 +1979,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020653</v>
+        <v>127020680</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>78777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,42 +1990,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729926</v>
+        <v>729872</v>
       </c>
       <c r="R15" t="n">
-        <v>7217876</v>
+        <v>7217916</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,17 +2052,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2077,45 +2077,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020712</v>
+        <v>127020654</v>
       </c>
       <c r="B16" t="n">
-        <v>80156</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729961</v>
+        <v>729936</v>
       </c>
       <c r="R16" t="n">
-        <v>7217852</v>
+        <v>7217870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2148,6 +2156,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2174,27 +2187,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020702</v>
+        <v>127020712</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>80156</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2209,7 +2222,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729956</v>
+        <v>729961</v>
       </c>
       <c r="R17" t="n">
         <v>7217852</v>
@@ -2271,10 +2284,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020654</v>
+        <v>127020702</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2282,42 +2295,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729936</v>
+        <v>729956</v>
       </c>
       <c r="R18" t="n">
-        <v>7217870</v>
+        <v>7217852</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2350,11 +2355,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2770,45 +2770,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020675</v>
+        <v>127020645</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729977</v>
+        <v>729635</v>
       </c>
       <c r="R23" t="n">
-        <v>7217779</v>
+        <v>7218021</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2841,6 +2849,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2867,7 +2880,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020652</v>
+        <v>127020631</v>
       </c>
       <c r="B24" t="n">
         <v>57661</v>
@@ -2910,10 +2923,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729906</v>
+        <v>729898</v>
       </c>
       <c r="R24" t="n">
-        <v>7217885</v>
+        <v>7217887</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,7 +2990,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020645</v>
+        <v>127020652</v>
       </c>
       <c r="B25" t="n">
         <v>57661</v>
@@ -3010,7 +3023,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3020,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729635</v>
+        <v>729906</v>
       </c>
       <c r="R25" t="n">
-        <v>7218021</v>
+        <v>7217885</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3060,7 +3073,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack bild 2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3087,53 +3100,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020631</v>
+        <v>127020675</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729898</v>
+        <v>729977</v>
       </c>
       <c r="R26" t="n">
-        <v>7217887</v>
+        <v>7217779</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3166,11 +3171,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4287,42 +4287,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020663</v>
+        <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>57658</v>
+        <v>80156</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4330,10 +4325,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730859</v>
+        <v>730711</v>
       </c>
       <c r="R38" t="n">
-        <v>7217175</v>
+        <v>7217270</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4368,14 +4363,35 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran, hoppat över från sälg som stod mycket nära</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4392,37 +4408,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127020711</v>
+        <v>127020663</v>
       </c>
       <c r="B39" t="n">
-        <v>80156</v>
+        <v>57658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4430,10 +4451,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730711</v>
+        <v>730859</v>
       </c>
       <c r="R39" t="n">
-        <v>7217270</v>
+        <v>7217175</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4468,35 +4489,14 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gran, hoppat över från sälg som stod mycket nära</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020655</v>
+        <v>127020642</v>
       </c>
       <c r="B42" t="n">
-        <v>57821</v>
+        <v>91330</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730778</v>
+        <v>730729</v>
       </c>
       <c r="R42" t="n">
-        <v>7217220</v>
+        <v>7217314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,11 +4791,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4822,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020642</v>
+        <v>127020655</v>
       </c>
       <c r="B43" t="n">
-        <v>91330</v>
+        <v>57821</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4857,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730729</v>
+        <v>730778</v>
       </c>
       <c r="R43" t="n">
-        <v>7217314</v>
+        <v>7217220</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,6 +4888,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6111,32 +6111,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020708</v>
+        <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>80156</v>
+        <v>91626</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730721</v>
+        <v>730729</v>
       </c>
       <c r="R56" t="n">
-        <v>7217258</v>
+        <v>7217314</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6208,27 +6208,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020698</v>
+        <v>127020708</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>80156</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730776</v>
+        <v>730721</v>
       </c>
       <c r="R57" t="n">
-        <v>7217232</v>
+        <v>7217258</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,10 +6305,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020667</v>
+        <v>127020698</v>
       </c>
       <c r="B58" t="n">
-        <v>91626</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730729</v>
+        <v>730776</v>
       </c>
       <c r="R58" t="n">
-        <v>7217314</v>
+        <v>7217232</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -1089,7 +1089,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020704</v>
+        <v>127020692</v>
       </c>
       <c r="B6" t="n">
         <v>79018</v>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729985</v>
+        <v>729964</v>
       </c>
       <c r="R6" t="n">
-        <v>7217794</v>
+        <v>7217823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020692</v>
+        <v>127020704</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729964</v>
+        <v>729985</v>
       </c>
       <c r="R7" t="n">
-        <v>7217823</v>
+        <v>7217794</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020653</v>
+        <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>78777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,42 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729926</v>
+        <v>729872</v>
       </c>
       <c r="R14" t="n">
-        <v>7217876</v>
+        <v>7217916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,17 +1942,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1979,10 +1967,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020680</v>
+        <v>127020653</v>
       </c>
       <c r="B15" t="n">
-        <v>78777</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1990,34 +1978,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729872</v>
+        <v>729926</v>
       </c>
       <c r="R15" t="n">
-        <v>7217916</v>
+        <v>7217876</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,13 +2048,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020671</v>
+        <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>58492</v>
+        <v>80156</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,21 +2586,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208245</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730037</v>
+        <v>729972</v>
       </c>
       <c r="R21" t="n">
-        <v>7217806</v>
+        <v>7217816</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,7 +2654,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2673,10 +2672,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020713</v>
+        <v>127020671</v>
       </c>
       <c r="B22" t="n">
-        <v>80156</v>
+        <v>58492</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2684,21 +2683,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>208245</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2708,10 +2707,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729972</v>
+        <v>730037</v>
       </c>
       <c r="R22" t="n">
-        <v>7217816</v>
+        <v>7217806</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2752,6 +2751,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2990,53 +2990,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020652</v>
+        <v>127020675</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729906</v>
+        <v>729977</v>
       </c>
       <c r="R25" t="n">
-        <v>7217885</v>
+        <v>7217779</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,11 +3061,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3100,45 +3087,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020675</v>
+        <v>127020652</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729977</v>
+        <v>729906</v>
       </c>
       <c r="R26" t="n">
-        <v>7217779</v>
+        <v>7217885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,6 +3166,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4287,37 +4287,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020711</v>
+        <v>127020663</v>
       </c>
       <c r="B38" t="n">
-        <v>80156</v>
+        <v>57658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4325,10 +4330,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730711</v>
+        <v>730859</v>
       </c>
       <c r="R38" t="n">
-        <v>7217270</v>
+        <v>7217175</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4363,35 +4368,14 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran, hoppat över från sälg som stod mycket nära</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4408,42 +4392,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127020663</v>
+        <v>127020711</v>
       </c>
       <c r="B39" t="n">
-        <v>57658</v>
+        <v>80156</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4451,10 +4430,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730859</v>
+        <v>730711</v>
       </c>
       <c r="R39" t="n">
-        <v>7217175</v>
+        <v>7217270</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4489,14 +4468,35 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gran, hoppat över från sälg som stod mycket nära</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -6111,32 +6111,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020667</v>
+        <v>127020708</v>
       </c>
       <c r="B56" t="n">
-        <v>91626</v>
+        <v>80156</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730729</v>
+        <v>730721</v>
       </c>
       <c r="R56" t="n">
-        <v>7217314</v>
+        <v>7217258</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6208,27 +6208,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020708</v>
+        <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>80156</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730721</v>
+        <v>730776</v>
       </c>
       <c r="R57" t="n">
-        <v>7217258</v>
+        <v>7217232</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,10 +6305,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020698</v>
+        <v>127020667</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>91626</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730776</v>
+        <v>730729</v>
       </c>
       <c r="R58" t="n">
-        <v>7217232</v>
+        <v>7217314</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020629</v>
+        <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729893</v>
+        <v>729985</v>
       </c>
       <c r="R4" t="n">
-        <v>7217893</v>
+        <v>7217794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127020706</v>
+        <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,42 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729913</v>
+        <v>729964</v>
       </c>
       <c r="R5" t="n">
-        <v>7217887</v>
+        <v>7217823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020692</v>
+        <v>127020629</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1074,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729964</v>
+        <v>729893</v>
       </c>
       <c r="R6" t="n">
-        <v>7217823</v>
+        <v>7217893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020704</v>
+        <v>127020706</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,34 +1184,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729985</v>
+        <v>729913</v>
       </c>
       <c r="R7" t="n">
-        <v>7217794</v>
+        <v>7217887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,6 +1252,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020644</v>
+        <v>127020680</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,37 +1779,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729994</v>
+        <v>729872</v>
       </c>
       <c r="R13" t="n">
-        <v>7217784</v>
+        <v>7217916</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1869,10 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020680</v>
+        <v>127020653</v>
       </c>
       <c r="B14" t="n">
-        <v>78777</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1877,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729872</v>
+        <v>729926</v>
       </c>
       <c r="R14" t="n">
-        <v>7217916</v>
+        <v>7217876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1942,13 +1947,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1967,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020653</v>
+        <v>127020644</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,31 +1987,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2010,10 +2014,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729926</v>
+        <v>729994</v>
       </c>
       <c r="R15" t="n">
-        <v>7217876</v>
+        <v>7217784</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,17 +2052,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2077,53 +2077,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020654</v>
+        <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>80156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729936</v>
+        <v>729961</v>
       </c>
       <c r="R16" t="n">
-        <v>7217870</v>
+        <v>7217852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2156,11 +2148,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2187,27 +2174,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020712</v>
+        <v>127020702</v>
       </c>
       <c r="B17" t="n">
-        <v>80156</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2222,7 +2209,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729961</v>
+        <v>729956</v>
       </c>
       <c r="R17" t="n">
         <v>7217852</v>
@@ -2284,10 +2271,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020702</v>
+        <v>127020654</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2295,34 +2282,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729956</v>
+        <v>729936</v>
       </c>
       <c r="R18" t="n">
-        <v>7217852</v>
+        <v>7217870</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,6 +2350,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2990,45 +2990,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020675</v>
+        <v>127020652</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729977</v>
+        <v>729906</v>
       </c>
       <c r="R25" t="n">
-        <v>7217779</v>
+        <v>7217885</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3061,6 +3069,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3087,53 +3100,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020652</v>
+        <v>127020675</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729906</v>
+        <v>729977</v>
       </c>
       <c r="R26" t="n">
-        <v>7217885</v>
+        <v>7217779</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3166,11 +3171,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3983,32 +3983,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020661</v>
+        <v>127020700</v>
       </c>
       <c r="B35" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730715</v>
+        <v>731060</v>
       </c>
       <c r="R35" t="n">
-        <v>7217263</v>
+        <v>7217069</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4080,32 +4080,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020700</v>
+        <v>127020661</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731060</v>
+        <v>730715</v>
       </c>
       <c r="R36" t="n">
-        <v>7217069</v>
+        <v>7217263</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4287,42 +4287,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020663</v>
+        <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>57658</v>
+        <v>80156</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4330,10 +4325,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730859</v>
+        <v>730711</v>
       </c>
       <c r="R38" t="n">
-        <v>7217175</v>
+        <v>7217270</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4368,14 +4363,35 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran, hoppat över från sälg som stod mycket nära</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4392,37 +4408,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127020711</v>
+        <v>127020663</v>
       </c>
       <c r="B39" t="n">
-        <v>80156</v>
+        <v>57658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4430,10 +4451,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730711</v>
+        <v>730859</v>
       </c>
       <c r="R39" t="n">
-        <v>7217270</v>
+        <v>7217175</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4468,35 +4489,14 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gran, hoppat över från sälg som stod mycket nära</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020642</v>
+        <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>91330</v>
+        <v>57821</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730729</v>
+        <v>730778</v>
       </c>
       <c r="R42" t="n">
-        <v>7217314</v>
+        <v>7217220</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,6 +4791,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020655</v>
+        <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>57821</v>
+        <v>91330</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4833,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730778</v>
+        <v>730729</v>
       </c>
       <c r="R43" t="n">
-        <v>7217220</v>
+        <v>7217314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,11 +4893,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6499,10 +6499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020668</v>
+        <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>97331</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>731110</v>
+        <v>730717</v>
       </c>
       <c r="R60" t="n">
-        <v>7217020</v>
+        <v>7217269</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020659</v>
+        <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>80150</v>
+        <v>97331</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,21 +6607,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730717</v>
+        <v>731110</v>
       </c>
       <c r="R61" t="n">
-        <v>7217269</v>
+        <v>7217020</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -2770,53 +2770,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020645</v>
+        <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729635</v>
+        <v>729977</v>
       </c>
       <c r="R23" t="n">
-        <v>7218021</v>
+        <v>7217779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,11 +2841,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2880,7 +2867,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020631</v>
+        <v>127020645</v>
       </c>
       <c r="B24" t="n">
         <v>57661</v>
@@ -2913,7 +2900,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2923,10 +2910,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729898</v>
+        <v>729635</v>
       </c>
       <c r="R24" t="n">
-        <v>7217887</v>
+        <v>7218021</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2963,7 +2950,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2990,7 +2977,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020652</v>
+        <v>127020631</v>
       </c>
       <c r="B25" t="n">
         <v>57661</v>
@@ -3033,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729906</v>
+        <v>729898</v>
       </c>
       <c r="R25" t="n">
-        <v>7217885</v>
+        <v>7217887</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3100,45 +3087,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020675</v>
+        <v>127020652</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729977</v>
+        <v>729906</v>
       </c>
       <c r="R26" t="n">
-        <v>7217779</v>
+        <v>7217885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,6 +3166,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020639</v>
+        <v>127020679</v>
       </c>
       <c r="B27" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729901</v>
+        <v>729853</v>
       </c>
       <c r="R27" t="n">
-        <v>7217877</v>
+        <v>7217932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,6 +3276,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3294,10 +3295,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020705</v>
+        <v>127020639</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3305,21 +3306,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3329,10 +3330,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729987</v>
+        <v>729901</v>
       </c>
       <c r="R28" t="n">
-        <v>7217772</v>
+        <v>7217877</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3391,10 +3392,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020679</v>
+        <v>127020705</v>
       </c>
       <c r="B29" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3402,21 +3403,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3426,10 +3427,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>729853</v>
+        <v>729987</v>
       </c>
       <c r="R29" t="n">
-        <v>7217932</v>
+        <v>7217772</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,7 +3471,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4513,45 +4513,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020674</v>
+        <v>127020648</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>731014</v>
+        <v>730971</v>
       </c>
       <c r="R40" t="n">
-        <v>7217177</v>
+        <v>7217152</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4584,6 +4592,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4610,53 +4623,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020648</v>
+        <v>127020674</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730971</v>
+        <v>731014</v>
       </c>
       <c r="R41" t="n">
-        <v>7217152</v>
+        <v>7217177</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,11 +4694,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020665</v>
       </c>
       <c r="B2" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127020670</v>
       </c>
       <c r="B3" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020704</v>
+        <v>127020629</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729985</v>
+        <v>729893</v>
       </c>
       <c r="R4" t="n">
-        <v>7217794</v>
+        <v>7217893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127020692</v>
+        <v>127020706</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +990,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729964</v>
+        <v>729913</v>
       </c>
       <c r="R5" t="n">
-        <v>7217823</v>
+        <v>7217887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020629</v>
+        <v>127020704</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,42 +1100,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729893</v>
+        <v>729985</v>
       </c>
       <c r="R6" t="n">
-        <v>7217893</v>
+        <v>7217794</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,11 +1160,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020706</v>
+        <v>127020692</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,42 +1197,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729913</v>
+        <v>729964</v>
       </c>
       <c r="R7" t="n">
-        <v>7217887</v>
+        <v>7217823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,11 +1257,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,7 +1286,7 @@
         <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020637</v>
+        <v>127020693</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729482</v>
+        <v>729531</v>
       </c>
       <c r="R10" t="n">
-        <v>7218068</v>
+        <v>7218052</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020693</v>
+        <v>127020688</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>91493</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729531</v>
+        <v>729734</v>
       </c>
       <c r="R11" t="n">
-        <v>7218052</v>
+        <v>7217951</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,32 +1671,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020688</v>
+        <v>127020637</v>
       </c>
       <c r="B12" t="n">
-        <v>91491</v>
+        <v>79638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729734</v>
+        <v>729482</v>
       </c>
       <c r="R12" t="n">
-        <v>7217951</v>
+        <v>7218068</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
         <v>127020680</v>
       </c>
       <c r="B13" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020653</v>
+        <v>127020644</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1877,31 +1877,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1909,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729926</v>
+        <v>729994</v>
       </c>
       <c r="R14" t="n">
-        <v>7217876</v>
+        <v>7217784</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,17 +1942,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1976,10 +1967,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020644</v>
+        <v>127020653</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,26 +1978,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2014,10 +2010,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729994</v>
+        <v>729926</v>
       </c>
       <c r="R15" t="n">
-        <v>7217784</v>
+        <v>7217876</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,13 +2048,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2077,27 +2077,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020712</v>
+        <v>127020702</v>
       </c>
       <c r="B16" t="n">
-        <v>80156</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729961</v>
+        <v>729956</v>
       </c>
       <c r="R16" t="n">
         <v>7217852</v>
@@ -2174,27 +2174,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020702</v>
+        <v>127020712</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>80158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729956</v>
+        <v>729961</v>
       </c>
       <c r="R17" t="n">
         <v>7217852</v>
@@ -2274,7 +2274,7 @@
         <v>127020654</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020713</v>
+        <v>127020671</v>
       </c>
       <c r="B21" t="n">
-        <v>80156</v>
+        <v>58494</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,21 +2586,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>208245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>729972</v>
+        <v>730037</v>
       </c>
       <c r="R21" t="n">
-        <v>7217816</v>
+        <v>7217806</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,6 +2654,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2673,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020671</v>
+        <v>127020713</v>
       </c>
       <c r="B22" t="n">
-        <v>58492</v>
+        <v>80158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2683,21 +2684,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2707,10 +2708,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730037</v>
+        <v>729972</v>
       </c>
       <c r="R22" t="n">
-        <v>7217806</v>
+        <v>7217816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2751,7 +2752,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>127020645</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>127020631</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>127020652</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020679</v>
+        <v>127020705</v>
       </c>
       <c r="B27" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729853</v>
+        <v>729987</v>
       </c>
       <c r="R27" t="n">
-        <v>7217932</v>
+        <v>7217772</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,7 +3276,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3298,7 +3297,7 @@
         <v>127020639</v>
       </c>
       <c r="B28" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3392,10 +3391,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020705</v>
+        <v>127020679</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3403,21 +3402,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3427,10 +3426,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>729987</v>
+        <v>729853</v>
       </c>
       <c r="R29" t="n">
-        <v>7217772</v>
+        <v>7217932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3471,6 +3470,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>127020666</v>
       </c>
       <c r="B30" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>75134</v>
+        <v>75136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>127020658</v>
       </c>
       <c r="B32" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>127020635</v>
       </c>
       <c r="B33" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>127020694</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>127020700</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>127020661</v>
       </c>
       <c r="B36" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>127020646</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>127020663</v>
       </c>
       <c r="B39" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4513,53 +4513,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020648</v>
+        <v>127020674</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>80151</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730971</v>
+        <v>731014</v>
       </c>
       <c r="R40" t="n">
-        <v>7217152</v>
+        <v>7217177</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4592,11 +4584,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4623,45 +4610,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020674</v>
+        <v>127020648</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>731014</v>
+        <v>730971</v>
       </c>
       <c r="R41" t="n">
-        <v>7217177</v>
+        <v>7217152</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4694,6 +4689,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4723,7 +4723,7 @@
         <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>127020647</v>
       </c>
       <c r="B44" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5029,10 +5029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127020691</v>
+        <v>127020701</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730593</v>
+        <v>730947</v>
       </c>
       <c r="R45" t="n">
-        <v>7217363</v>
+        <v>7217151</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5100,11 +5100,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>6st långa bålar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5134,7 +5129,7 @@
         <v>127020699</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5228,10 +5223,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020701</v>
+        <v>127020691</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5263,10 +5258,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730947</v>
+        <v>730593</v>
       </c>
       <c r="R47" t="n">
-        <v>7217151</v>
+        <v>7217363</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5299,6 +5294,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>6st långa bålar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5328,7 +5328,7 @@
         <v>127020697</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>127020689</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>127020695</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>127020690</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>127020696</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6111,32 +6111,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020708</v>
+        <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>80156</v>
+        <v>91628</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730721</v>
+        <v>730729</v>
       </c>
       <c r="R56" t="n">
-        <v>7217258</v>
+        <v>7217314</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6211,7 +6211,7 @@
         <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6305,32 +6305,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020667</v>
+        <v>127020708</v>
       </c>
       <c r="B58" t="n">
-        <v>91626</v>
+        <v>80158</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730729</v>
+        <v>730721</v>
       </c>
       <c r="R58" t="n">
-        <v>7217314</v>
+        <v>7217258</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6405,7 +6405,7 @@
         <v>127020660</v>
       </c>
       <c r="B59" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020629</v>
+        <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729893</v>
+        <v>729985</v>
       </c>
       <c r="R4" t="n">
-        <v>7217893</v>
+        <v>7217794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127020706</v>
+        <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,42 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729913</v>
+        <v>729964</v>
       </c>
       <c r="R5" t="n">
-        <v>7217887</v>
+        <v>7217823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020704</v>
+        <v>127020629</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1074,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729985</v>
+        <v>729893</v>
       </c>
       <c r="R6" t="n">
-        <v>7217794</v>
+        <v>7217893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020692</v>
+        <v>127020706</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,34 +1184,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729964</v>
+        <v>729913</v>
       </c>
       <c r="R7" t="n">
-        <v>7217823</v>
+        <v>7217887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,6 +1252,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127020664</v>
+        <v>127020662</v>
       </c>
       <c r="B8" t="n">
-        <v>80027</v>
+        <v>80152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,21 +1294,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729960</v>
+        <v>729959</v>
       </c>
       <c r="R8" t="n">
-        <v>7217849</v>
+        <v>7217826</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127020662</v>
+        <v>127020664</v>
       </c>
       <c r="B9" t="n">
-        <v>80152</v>
+        <v>80027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,21 +1391,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729959</v>
+        <v>729960</v>
       </c>
       <c r="R9" t="n">
-        <v>7217826</v>
+        <v>7217849</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,32 +1477,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020693</v>
+        <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>91493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729531</v>
+        <v>729734</v>
       </c>
       <c r="R10" t="n">
-        <v>7218052</v>
+        <v>7217951</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,32 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020688</v>
+        <v>127020637</v>
       </c>
       <c r="B11" t="n">
-        <v>91493</v>
+        <v>79638</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729734</v>
+        <v>729482</v>
       </c>
       <c r="R11" t="n">
-        <v>7217951</v>
+        <v>7218068</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020637</v>
+        <v>127020693</v>
       </c>
       <c r="B12" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1682,21 +1682,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729482</v>
+        <v>729531</v>
       </c>
       <c r="R12" t="n">
-        <v>7218068</v>
+        <v>7218052</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020680</v>
+        <v>127020644</v>
       </c>
       <c r="B13" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,34 +1779,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729872</v>
+        <v>729994</v>
       </c>
       <c r="R13" t="n">
-        <v>7217916</v>
+        <v>7217784</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020644</v>
+        <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1877,37 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729994</v>
+        <v>729872</v>
       </c>
       <c r="R14" t="n">
-        <v>7217784</v>
+        <v>7217916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020671</v>
+        <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>58494</v>
+        <v>80158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,21 +2586,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208245</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730037</v>
+        <v>729972</v>
       </c>
       <c r="R21" t="n">
-        <v>7217806</v>
+        <v>7217816</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,7 +2654,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2673,10 +2672,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020713</v>
+        <v>127020671</v>
       </c>
       <c r="B22" t="n">
-        <v>80158</v>
+        <v>58494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2684,21 +2683,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>208245</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2708,10 +2707,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729972</v>
+        <v>730037</v>
       </c>
       <c r="R22" t="n">
-        <v>7217816</v>
+        <v>7217806</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2752,6 +2751,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -4080,45 +4080,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020661</v>
+        <v>127020646</v>
       </c>
       <c r="B36" t="n">
-        <v>80152</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730715</v>
+        <v>731050</v>
       </c>
       <c r="R36" t="n">
-        <v>7217263</v>
+        <v>7217071</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4151,6 +4159,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4177,53 +4190,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020646</v>
+        <v>127020661</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>80152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>731050</v>
+        <v>730715</v>
       </c>
       <c r="R37" t="n">
-        <v>7217071</v>
+        <v>7217263</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4256,11 +4261,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4287,37 +4287,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020711</v>
+        <v>127020663</v>
       </c>
       <c r="B38" t="n">
-        <v>80158</v>
+        <v>57660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4325,10 +4330,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730711</v>
+        <v>730859</v>
       </c>
       <c r="R38" t="n">
-        <v>7217270</v>
+        <v>7217175</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4363,35 +4368,14 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran, hoppat över från sälg som stod mycket nära</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4408,42 +4392,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127020663</v>
+        <v>127020711</v>
       </c>
       <c r="B39" t="n">
-        <v>57660</v>
+        <v>80158</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4451,10 +4430,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730859</v>
+        <v>730711</v>
       </c>
       <c r="R39" t="n">
-        <v>7217175</v>
+        <v>7217270</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4489,14 +4468,35 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gran, hoppat över från sälg som stod mycket nära</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020655</v>
+        <v>127020642</v>
       </c>
       <c r="B42" t="n">
-        <v>57823</v>
+        <v>91332</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730778</v>
+        <v>730729</v>
       </c>
       <c r="R42" t="n">
-        <v>7217220</v>
+        <v>7217314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,11 +4791,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4822,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020642</v>
+        <v>127020655</v>
       </c>
       <c r="B43" t="n">
-        <v>91332</v>
+        <v>57823</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4857,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730729</v>
+        <v>730778</v>
       </c>
       <c r="R43" t="n">
-        <v>7217314</v>
+        <v>7217220</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,6 +4888,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5029,7 +5029,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127020701</v>
+        <v>127020691</v>
       </c>
       <c r="B45" t="n">
         <v>79020</v>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730947</v>
+        <v>730593</v>
       </c>
       <c r="R45" t="n">
-        <v>7217151</v>
+        <v>7217363</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5100,6 +5100,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>6st långa bålar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5223,7 +5228,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020691</v>
+        <v>127020701</v>
       </c>
       <c r="B47" t="n">
         <v>79020</v>
@@ -5258,10 +5263,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730593</v>
+        <v>730947</v>
       </c>
       <c r="R47" t="n">
-        <v>7217363</v>
+        <v>7217151</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5294,11 +5299,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>6st långa bålar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5519,32 +5519,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020710</v>
+        <v>127020632</v>
       </c>
       <c r="B50" t="n">
-        <v>80158</v>
+        <v>75144</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730874</v>
+        <v>730709</v>
       </c>
       <c r="R50" t="n">
-        <v>7217193</v>
+        <v>7217283</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5616,32 +5616,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020632</v>
+        <v>127020710</v>
       </c>
       <c r="B51" t="n">
-        <v>75144</v>
+        <v>80158</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730709</v>
+        <v>730874</v>
       </c>
       <c r="R51" t="n">
-        <v>7217283</v>
+        <v>7217193</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020644</v>
+        <v>127020653</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,26 +1779,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1806,10 +1811,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729994</v>
+        <v>729926</v>
       </c>
       <c r="R13" t="n">
-        <v>7217784</v>
+        <v>7217876</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,13 +1849,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1967,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020653</v>
+        <v>127020644</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,31 +1987,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2010,10 +2014,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729926</v>
+        <v>729994</v>
       </c>
       <c r="R15" t="n">
-        <v>7217876</v>
+        <v>7217784</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,17 +2052,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2770,45 +2770,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020675</v>
+        <v>127020631</v>
       </c>
       <c r="B23" t="n">
-        <v>80151</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729977</v>
+        <v>729898</v>
       </c>
       <c r="R23" t="n">
-        <v>7217779</v>
+        <v>7217887</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2841,6 +2849,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2867,53 +2880,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020645</v>
+        <v>127020675</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>80151</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729635</v>
+        <v>729977</v>
       </c>
       <c r="R24" t="n">
-        <v>7218021</v>
+        <v>7217779</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2946,11 +2951,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2977,7 +2977,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020631</v>
+        <v>127020645</v>
       </c>
       <c r="B25" t="n">
         <v>57663</v>
@@ -3010,7 +3010,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729898</v>
+        <v>729635</v>
       </c>
       <c r="R25" t="n">
-        <v>7217887</v>
+        <v>7218021</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020704</v>
+        <v>127020629</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729985</v>
+        <v>729893</v>
       </c>
       <c r="R4" t="n">
-        <v>7217794</v>
+        <v>7217893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127020692</v>
+        <v>127020706</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +990,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729964</v>
+        <v>729913</v>
       </c>
       <c r="R5" t="n">
-        <v>7217823</v>
+        <v>7217887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020629</v>
+        <v>127020704</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,42 +1100,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729893</v>
+        <v>729985</v>
       </c>
       <c r="R6" t="n">
-        <v>7217893</v>
+        <v>7217794</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,11 +1160,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020706</v>
+        <v>127020692</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,42 +1197,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729913</v>
+        <v>729964</v>
       </c>
       <c r="R7" t="n">
-        <v>7217887</v>
+        <v>7217823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,11 +1257,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127020662</v>
+        <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80152</v>
+        <v>80027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,21 +1294,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729959</v>
+        <v>729960</v>
       </c>
       <c r="R8" t="n">
-        <v>7217826</v>
+        <v>7217849</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127020664</v>
+        <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>80027</v>
+        <v>80152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,21 +1391,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729960</v>
+        <v>729959</v>
       </c>
       <c r="R9" t="n">
-        <v>7217849</v>
+        <v>7217826</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020653</v>
+        <v>127020644</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,31 +1779,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1811,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729926</v>
+        <v>729994</v>
       </c>
       <c r="R13" t="n">
-        <v>7217876</v>
+        <v>7217784</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,17 +1844,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1878,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020680</v>
+        <v>127020653</v>
       </c>
       <c r="B14" t="n">
-        <v>78779</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,34 +1880,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729872</v>
+        <v>729926</v>
       </c>
       <c r="R14" t="n">
-        <v>7217916</v>
+        <v>7217876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,13 +1950,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1976,10 +1979,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020644</v>
+        <v>127020680</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,37 +1990,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729994</v>
+        <v>729872</v>
       </c>
       <c r="R15" t="n">
-        <v>7217784</v>
+        <v>7217916</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2770,53 +2770,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020631</v>
+        <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>80151</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729898</v>
+        <v>729977</v>
       </c>
       <c r="R23" t="n">
-        <v>7217887</v>
+        <v>7217779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,11 +2841,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2880,45 +2867,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020675</v>
+        <v>127020645</v>
       </c>
       <c r="B24" t="n">
-        <v>80151</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729977</v>
+        <v>729635</v>
       </c>
       <c r="R24" t="n">
-        <v>7217779</v>
+        <v>7218021</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,6 +2946,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2977,7 +2977,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020645</v>
+        <v>127020631</v>
       </c>
       <c r="B25" t="n">
         <v>57663</v>
@@ -3010,7 +3010,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729635</v>
+        <v>729898</v>
       </c>
       <c r="R25" t="n">
-        <v>7218021</v>
+        <v>7217887</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack bild 2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020705</v>
+        <v>127020679</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729987</v>
+        <v>729853</v>
       </c>
       <c r="R27" t="n">
-        <v>7217772</v>
+        <v>7217932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,6 +3276,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3294,10 +3295,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020639</v>
+        <v>127020705</v>
       </c>
       <c r="B28" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3305,21 +3306,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3329,10 +3330,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729901</v>
+        <v>729987</v>
       </c>
       <c r="R28" t="n">
-        <v>7217877</v>
+        <v>7217772</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3391,10 +3392,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020679</v>
+        <v>127020639</v>
       </c>
       <c r="B29" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3402,21 +3403,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3426,10 +3427,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>729853</v>
+        <v>729901</v>
       </c>
       <c r="R29" t="n">
-        <v>7217932</v>
+        <v>7217877</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,7 +3471,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4080,53 +4080,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020646</v>
+        <v>127020661</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>80152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731050</v>
+        <v>730715</v>
       </c>
       <c r="R36" t="n">
-        <v>7217071</v>
+        <v>7217263</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4159,11 +4151,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4190,45 +4177,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020661</v>
+        <v>127020646</v>
       </c>
       <c r="B37" t="n">
-        <v>80152</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730715</v>
+        <v>731050</v>
       </c>
       <c r="R37" t="n">
-        <v>7217263</v>
+        <v>7217071</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4261,6 +4256,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5519,32 +5519,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020632</v>
+        <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>75144</v>
+        <v>80158</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730709</v>
+        <v>730874</v>
       </c>
       <c r="R50" t="n">
-        <v>7217283</v>
+        <v>7217193</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5616,32 +5616,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020710</v>
+        <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>80158</v>
+        <v>75144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730874</v>
+        <v>730709</v>
       </c>
       <c r="R51" t="n">
-        <v>7217193</v>
+        <v>7217283</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6111,10 +6111,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020667</v>
+        <v>127020698</v>
       </c>
       <c r="B56" t="n">
-        <v>91628</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6122,21 +6122,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730729</v>
+        <v>730776</v>
       </c>
       <c r="R56" t="n">
-        <v>7217314</v>
+        <v>7217232</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6208,27 +6208,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020698</v>
+        <v>127020708</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>80158</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730776</v>
+        <v>730721</v>
       </c>
       <c r="R57" t="n">
-        <v>7217232</v>
+        <v>7217258</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,32 +6305,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020708</v>
+        <v>127020667</v>
       </c>
       <c r="B58" t="n">
-        <v>80158</v>
+        <v>91628</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730721</v>
+        <v>730729</v>
       </c>
       <c r="R58" t="n">
-        <v>7217258</v>
+        <v>7217314</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127020665</v>
+        <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>80027</v>
+        <v>97339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730028</v>
+        <v>729978</v>
       </c>
       <c r="R2" t="n">
-        <v>7217812</v>
+        <v>7217767</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127020670</v>
+        <v>127020665</v>
       </c>
       <c r="B3" t="n">
-        <v>97333</v>
+        <v>80027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729978</v>
+        <v>730028</v>
       </c>
       <c r="R3" t="n">
-        <v>7217767</v>
+        <v>7217812</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020629</v>
+        <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729893</v>
+        <v>729985</v>
       </c>
       <c r="R4" t="n">
-        <v>7217893</v>
+        <v>7217794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127020706</v>
+        <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,42 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729913</v>
+        <v>729964</v>
       </c>
       <c r="R5" t="n">
-        <v>7217887</v>
+        <v>7217823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020704</v>
+        <v>127020629</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1074,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729985</v>
+        <v>729893</v>
       </c>
       <c r="R6" t="n">
-        <v>7217794</v>
+        <v>7217893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020692</v>
+        <v>127020706</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,34 +1184,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729964</v>
+        <v>729913</v>
       </c>
       <c r="R7" t="n">
-        <v>7217823</v>
+        <v>7217887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,6 +1252,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1480,7 +1480,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91493</v>
+        <v>91499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020637</v>
+        <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729482</v>
+        <v>729531</v>
       </c>
       <c r="R11" t="n">
-        <v>7218068</v>
+        <v>7218052</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020693</v>
+        <v>127020637</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1682,21 +1682,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729531</v>
+        <v>729482</v>
       </c>
       <c r="R12" t="n">
-        <v>7218052</v>
+        <v>7218068</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020644</v>
+        <v>127020653</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,26 +1779,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1806,10 +1811,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729994</v>
+        <v>729926</v>
       </c>
       <c r="R13" t="n">
-        <v>7217784</v>
+        <v>7217876</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,13 +1849,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1869,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020653</v>
+        <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>78779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,42 +1889,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729926</v>
+        <v>729872</v>
       </c>
       <c r="R14" t="n">
-        <v>7217876</v>
+        <v>7217916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,17 +1951,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1979,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020680</v>
+        <v>127020644</v>
       </c>
       <c r="B15" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1990,34 +1987,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729872</v>
+        <v>729994</v>
       </c>
       <c r="R15" t="n">
-        <v>7217916</v>
+        <v>7217784</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,27 +2077,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020702</v>
+        <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>80158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729956</v>
+        <v>729961</v>
       </c>
       <c r="R16" t="n">
         <v>7217852</v>
@@ -2174,27 +2174,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020712</v>
+        <v>127020702</v>
       </c>
       <c r="B17" t="n">
-        <v>80158</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729961</v>
+        <v>729956</v>
       </c>
       <c r="R17" t="n">
         <v>7217852</v>
@@ -2384,7 +2384,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4080,45 +4080,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020661</v>
+        <v>127020646</v>
       </c>
       <c r="B36" t="n">
-        <v>80152</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730715</v>
+        <v>731050</v>
       </c>
       <c r="R36" t="n">
-        <v>7217263</v>
+        <v>7217071</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4151,6 +4159,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4177,53 +4190,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020646</v>
+        <v>127020661</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>80152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>731050</v>
+        <v>730715</v>
       </c>
       <c r="R37" t="n">
-        <v>7217071</v>
+        <v>7217263</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4256,11 +4261,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4287,42 +4287,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020663</v>
+        <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>57660</v>
+        <v>80158</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4330,10 +4325,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730859</v>
+        <v>730711</v>
       </c>
       <c r="R38" t="n">
-        <v>7217175</v>
+        <v>7217270</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4368,14 +4363,35 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran, hoppat över från sälg som stod mycket nära</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4392,37 +4408,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127020711</v>
+        <v>127020663</v>
       </c>
       <c r="B39" t="n">
-        <v>80158</v>
+        <v>57660</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4430,10 +4451,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730711</v>
+        <v>730859</v>
       </c>
       <c r="R39" t="n">
-        <v>7217270</v>
+        <v>7217175</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4468,35 +4489,14 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gran, hoppat över från sälg som stod mycket nära</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4513,45 +4513,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020674</v>
+        <v>127020648</v>
       </c>
       <c r="B40" t="n">
-        <v>80151</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>731014</v>
+        <v>730971</v>
       </c>
       <c r="R40" t="n">
-        <v>7217177</v>
+        <v>7217152</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4584,6 +4592,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4610,53 +4623,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020648</v>
+        <v>127020674</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>80151</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730971</v>
+        <v>731014</v>
       </c>
       <c r="R41" t="n">
-        <v>7217152</v>
+        <v>7217177</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,11 +4694,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020642</v>
+        <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>91332</v>
+        <v>57823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730729</v>
+        <v>730778</v>
       </c>
       <c r="R42" t="n">
-        <v>7217314</v>
+        <v>7217220</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,6 +4791,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020655</v>
+        <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>57823</v>
+        <v>91338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4833,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730778</v>
+        <v>730729</v>
       </c>
       <c r="R43" t="n">
-        <v>7217220</v>
+        <v>7217314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,11 +4893,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5818,7 +5818,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6111,10 +6111,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020698</v>
+        <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>91634</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6122,21 +6122,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730776</v>
+        <v>730729</v>
       </c>
       <c r="R56" t="n">
-        <v>7217232</v>
+        <v>7217314</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6208,27 +6208,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020708</v>
+        <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>80158</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730721</v>
+        <v>730776</v>
       </c>
       <c r="R57" t="n">
-        <v>7217258</v>
+        <v>7217232</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,32 +6305,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020667</v>
+        <v>127020708</v>
       </c>
       <c r="B58" t="n">
-        <v>91628</v>
+        <v>80158</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730729</v>
+        <v>730721</v>
       </c>
       <c r="R58" t="n">
-        <v>7217314</v>
+        <v>7217258</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6599,7 +6599,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97339</v>
+        <v>97509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127020665</v>
       </c>
       <c r="B3" t="n">
-        <v>80027</v>
+        <v>80129</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,14 +970,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1071,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127020629</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,14 +1185,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127020706</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,14 +1299,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80027</v>
+        <v>80129</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,14 +1400,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>80152</v>
+        <v>80254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,14 +1501,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91499</v>
+        <v>91665</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,14 +1602,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,14 +1703,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127020637</v>
       </c>
       <c r="B12" t="n">
-        <v>79638</v>
+        <v>79739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,14 +1804,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127020653</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,14 +1918,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>78779</v>
+        <v>78878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,14 +2020,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127020644</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,14 +2125,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>80158</v>
+        <v>80260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2170,14 +2226,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127020702</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2267,14 +2327,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>127020654</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,14 +2441,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>92821</v>
+        <v>92989</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,14 +2542,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91303</v>
+        <v>91469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,14 +2643,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>80158</v>
+        <v>80260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,14 +2744,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>127020671</v>
       </c>
       <c r="B22" t="n">
-        <v>58494</v>
+        <v>58547</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,14 +2846,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>80151</v>
+        <v>80253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,14 +2947,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>127020645</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,14 +3061,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>127020631</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3083,14 +3175,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>127020652</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3193,14 +3289,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>127020679</v>
       </c>
       <c r="B27" t="n">
-        <v>78779</v>
+        <v>78878</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,14 +3391,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>127020705</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3388,14 +3492,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>127020639</v>
       </c>
       <c r="B29" t="n">
-        <v>79638</v>
+        <v>79739</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3485,14 +3593,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>127020666</v>
       </c>
       <c r="B30" t="n">
-        <v>80027</v>
+        <v>80129</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,14 +3694,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>75136</v>
+        <v>75197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3680,14 +3796,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>127020658</v>
       </c>
       <c r="B32" t="n">
-        <v>57823</v>
+        <v>57876</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3785,14 +3905,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>127020635</v>
       </c>
       <c r="B33" t="n">
-        <v>79638</v>
+        <v>79739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3882,14 +4006,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>127020694</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3979,14 +4107,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>127020700</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4076,14 +4208,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>127020646</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4186,14 +4322,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>127020661</v>
       </c>
       <c r="B37" t="n">
-        <v>80152</v>
+        <v>80254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4283,14 +4423,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>80158</v>
+        <v>80260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4404,14 +4548,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>127020663</v>
       </c>
       <c r="B39" t="n">
-        <v>57660</v>
+        <v>57713</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4509,14 +4657,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>127020648</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4619,14 +4771,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>127020674</v>
       </c>
       <c r="B41" t="n">
-        <v>80151</v>
+        <v>80253</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4716,14 +4872,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>57823</v>
+        <v>57876</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4818,14 +4978,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91338</v>
+        <v>91504</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4915,14 +5079,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>127020647</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5025,14 +5193,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>127020691</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5127,14 +5299,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>127020699</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5224,14 +5400,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>127020701</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5321,14 +5501,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>127020697</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5418,14 +5602,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>127020689</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5515,14 +5703,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>80158</v>
+        <v>80260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5612,14 +5804,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>75144</v>
+        <v>75205</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5709,14 +5905,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>127020695</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5811,14 +6011,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97339</v>
+        <v>97509</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5908,14 +6112,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>127020690</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6005,14 +6213,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>127020696</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6107,14 +6319,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91634</v>
+        <v>91800</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6204,14 +6420,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6301,14 +6521,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>127020708</v>
       </c>
       <c r="B58" t="n">
-        <v>80158</v>
+        <v>80260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6398,14 +6622,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>127020660</v>
       </c>
       <c r="B59" t="n">
-        <v>80152</v>
+        <v>80254</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6495,14 +6723,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>80152</v>
+        <v>80254</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6592,14 +6824,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97339</v>
+        <v>97509</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6689,7 +6925,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127020665</v>
       </c>
       <c r="B3" t="n">
-        <v>80129</v>
+        <v>80133</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127020629</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127020706</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80129</v>
+        <v>80133</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91665</v>
+        <v>91669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127020637</v>
       </c>
       <c r="B12" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127020653</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>127020644</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>127020702</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>127020654</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>127020671</v>
       </c>
       <c r="B22" t="n">
-        <v>58547</v>
+        <v>58551</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>127020645</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>127020631</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>127020652</v>
       </c>
       <c r="B26" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>127020679</v>
       </c>
       <c r="B27" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>127020705</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>127020639</v>
       </c>
       <c r="B29" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>127020666</v>
       </c>
       <c r="B30" t="n">
-        <v>80129</v>
+        <v>80133</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>75197</v>
+        <v>75201</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>127020658</v>
       </c>
       <c r="B32" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>127020635</v>
       </c>
       <c r="B33" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>127020694</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>127020700</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>127020646</v>
       </c>
       <c r="B36" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>127020661</v>
       </c>
       <c r="B37" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>127020663</v>
       </c>
       <c r="B39" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>127020648</v>
       </c>
       <c r="B40" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>127020674</v>
       </c>
       <c r="B41" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>127020647</v>
       </c>
       <c r="B44" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>127020691</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>127020699</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>127020701</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>127020697</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>127020689</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>127020695</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>127020690</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>127020696</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>127020708</v>
       </c>
       <c r="B58" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127020660</v>
       </c>
       <c r="B59" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127020665</v>
       </c>
       <c r="B3" t="n">
-        <v>80133</v>
+        <v>80038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127020629</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127020706</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80133</v>
+        <v>80038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91669</v>
+        <v>91674</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127020637</v>
       </c>
       <c r="B12" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127020653</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>127020644</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>127020702</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>127020654</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>127020671</v>
       </c>
       <c r="B22" t="n">
-        <v>58551</v>
+        <v>58554</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>127020645</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>127020631</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>127020652</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>127020679</v>
       </c>
       <c r="B27" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>127020705</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>127020639</v>
       </c>
       <c r="B29" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>127020666</v>
       </c>
       <c r="B30" t="n">
-        <v>80133</v>
+        <v>80038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>75201</v>
+        <v>82997</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>127020658</v>
       </c>
       <c r="B32" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>127020635</v>
       </c>
       <c r="B33" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>127020694</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>127020700</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>127020646</v>
       </c>
       <c r="B36" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>127020661</v>
       </c>
       <c r="B37" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>127020663</v>
       </c>
       <c r="B39" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>127020648</v>
       </c>
       <c r="B40" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>127020674</v>
       </c>
       <c r="B41" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>127020647</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>127020691</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>127020699</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>127020701</v>
       </c>
       <c r="B47" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>127020697</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>127020689</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>127020695</v>
       </c>
       <c r="B52" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>127020690</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>127020696</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>127020708</v>
       </c>
       <c r="B58" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127020660</v>
       </c>
       <c r="B59" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91681</v>
+        <v>91684</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127020665</v>
       </c>
       <c r="B3" t="n">
-        <v>80043</v>
+        <v>80044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80043</v>
+        <v>80044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91684</v>
+        <v>91687</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127020637</v>
       </c>
       <c r="B12" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>127020644</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>127020702</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>127020679</v>
       </c>
       <c r="B27" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>127020705</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>127020639</v>
       </c>
       <c r="B29" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>127020666</v>
       </c>
       <c r="B30" t="n">
-        <v>80043</v>
+        <v>80044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>83002</v>
+        <v>83003</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>127020635</v>
       </c>
       <c r="B33" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>127020694</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>127020700</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>127020661</v>
       </c>
       <c r="B37" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>127020674</v>
       </c>
       <c r="B41" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>127020691</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>127020699</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>127020701</v>
       </c>
       <c r="B47" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>127020697</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>127020689</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>127020695</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>127020690</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>127020696</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>127020708</v>
       </c>
       <c r="B58" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127020660</v>
       </c>
       <c r="B59" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127020665</v>
       </c>
       <c r="B3" t="n">
-        <v>80044</v>
+        <v>80048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127020629</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127020706</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80044</v>
+        <v>80048</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91687</v>
+        <v>91694</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127020637</v>
       </c>
       <c r="B12" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127020653</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>127020644</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>127020702</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>127020654</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>127020671</v>
       </c>
       <c r="B22" t="n">
-        <v>58554</v>
+        <v>58556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>127020645</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>127020631</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>127020652</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>127020679</v>
       </c>
       <c r="B27" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>127020705</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>127020639</v>
       </c>
       <c r="B29" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>127020666</v>
       </c>
       <c r="B30" t="n">
-        <v>80044</v>
+        <v>80048</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>83003</v>
+        <v>83007</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>127020658</v>
       </c>
       <c r="B32" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>127020635</v>
       </c>
       <c r="B33" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>127020694</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>127020700</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>127020646</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>127020661</v>
       </c>
       <c r="B37" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>127020663</v>
       </c>
       <c r="B39" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>127020648</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>127020674</v>
       </c>
       <c r="B41" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>127020647</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>127020691</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>127020699</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>127020701</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>127020697</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>127020689</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>127020695</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>127020690</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>127020696</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>127020708</v>
       </c>
       <c r="B58" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127020660</v>
       </c>
       <c r="B59" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91694</v>
+        <v>91701</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>83007</v>
+        <v>82997</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127020665</v>
       </c>
       <c r="B3" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127020629</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127020706</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127020637</v>
       </c>
       <c r="B12" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127020653</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>127020644</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>127020702</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>127020654</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>127020671</v>
       </c>
       <c r="B22" t="n">
-        <v>58556</v>
+        <v>58558</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>127020645</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>127020631</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>127020652</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>127020679</v>
       </c>
       <c r="B27" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>127020705</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>127020639</v>
       </c>
       <c r="B29" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>127020666</v>
       </c>
       <c r="B30" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>82997</v>
+        <v>82999</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>127020658</v>
       </c>
       <c r="B32" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>127020635</v>
       </c>
       <c r="B33" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>127020694</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>127020700</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>127020646</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>127020661</v>
       </c>
       <c r="B37" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>127020663</v>
       </c>
       <c r="B39" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>127020648</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>127020674</v>
       </c>
       <c r="B41" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>127020655</v>
       </c>
       <c r="B42" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>127020647</v>
       </c>
       <c r="B44" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>127020691</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>127020699</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>127020701</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>127020697</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>127020689</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>127020695</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>127020690</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>127020696</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>127020708</v>
       </c>
       <c r="B58" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127020660</v>
       </c>
       <c r="B59" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91703</v>
+        <v>91712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91712</v>
+        <v>91713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127020665</v>
       </c>
       <c r="B3" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127020637</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>127020644</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>127020702</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>127020679</v>
       </c>
       <c r="B27" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>127020705</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>127020639</v>
       </c>
       <c r="B29" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>127020666</v>
       </c>
       <c r="B30" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>82999</v>
+        <v>83003</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>127020635</v>
       </c>
       <c r="B33" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>127020694</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>127020700</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>127020661</v>
       </c>
       <c r="B37" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>127020674</v>
       </c>
       <c r="B41" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>127020691</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>127020699</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>127020701</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>127020697</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>127020689</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>127020695</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>127020690</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>127020696</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>127020708</v>
       </c>
       <c r="B58" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127020660</v>
       </c>
       <c r="B59" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127020665</v>
       </c>
       <c r="B3" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127020704</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127020692</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>127020664</v>
       </c>
       <c r="B8" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127020662</v>
       </c>
       <c r="B9" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91716</v>
+        <v>91718</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127020693</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127020637</v>
       </c>
       <c r="B12" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>127020680</v>
       </c>
       <c r="B14" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>127020644</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>127020712</v>
       </c>
       <c r="B16" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>127020702</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>127020713</v>
       </c>
       <c r="B21" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>127020679</v>
       </c>
       <c r="B27" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>127020705</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>127020639</v>
       </c>
       <c r="B29" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>127020666</v>
       </c>
       <c r="B30" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>127020672</v>
       </c>
       <c r="B31" t="n">
-        <v>83003</v>
+        <v>83004</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>127020635</v>
       </c>
       <c r="B33" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>127020694</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>127020700</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>127020661</v>
       </c>
       <c r="B37" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>127020711</v>
       </c>
       <c r="B38" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>127020674</v>
       </c>
       <c r="B41" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>127020691</v>
       </c>
       <c r="B45" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>127020699</v>
       </c>
       <c r="B46" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>127020701</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>127020697</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>127020689</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>127020710</v>
       </c>
       <c r="B50" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>127020632</v>
       </c>
       <c r="B51" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>127020695</v>
       </c>
       <c r="B52" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>127020690</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>127020696</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>127020698</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>127020708</v>
       </c>
       <c r="B58" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>127020660</v>
       </c>
       <c r="B59" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127020659</v>
       </c>
       <c r="B60" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020670</v>
       </c>
       <c r="B2" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127020688</v>
       </c>
       <c r="B10" t="n">
-        <v>91718</v>
+        <v>91722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>127020676</v>
       </c>
       <c r="B19" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127020634</v>
       </c>
       <c r="B20" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>127020669</v>
       </c>
       <c r="B53" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127020667</v>
       </c>
       <c r="B56" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>127020668</v>
       </c>
       <c r="B61" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127020670</v>
+        <v>127020665</v>
       </c>
       <c r="B2" t="n">
-        <v>97593</v>
+        <v>80053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729978</v>
+        <v>730028</v>
       </c>
       <c r="R2" t="n">
-        <v>7217767</v>
+        <v>7217812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127020665</v>
+        <v>127020670</v>
       </c>
       <c r="B3" t="n">
-        <v>80053</v>
+        <v>97593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730028</v>
+        <v>729978</v>
       </c>
       <c r="R3" t="n">
-        <v>7217812</v>
+        <v>7217767</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020704</v>
+        <v>127020629</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +888,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729985</v>
+        <v>729893</v>
       </c>
       <c r="R4" t="n">
-        <v>7217794</v>
+        <v>7217893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +956,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127020692</v>
+        <v>127020706</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,34 +1002,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729964</v>
+        <v>729913</v>
       </c>
       <c r="R5" t="n">
-        <v>7217823</v>
+        <v>7217887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,6 +1070,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020629</v>
+        <v>127020692</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,42 +1116,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729893</v>
+        <v>729964</v>
       </c>
       <c r="R6" t="n">
-        <v>7217893</v>
+        <v>7217823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,11 +1176,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020706</v>
+        <v>127020704</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,42 +1217,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729913</v>
+        <v>729985</v>
       </c>
       <c r="R7" t="n">
-        <v>7217887</v>
+        <v>7217794</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,11 +1277,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1509,32 +1509,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020688</v>
+        <v>127020637</v>
       </c>
       <c r="B10" t="n">
-        <v>91722</v>
+        <v>79663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729734</v>
+        <v>729482</v>
       </c>
       <c r="R10" t="n">
-        <v>7217951</v>
+        <v>7218068</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,32 +1711,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020637</v>
+        <v>127020688</v>
       </c>
       <c r="B12" t="n">
-        <v>79663</v>
+        <v>91722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1746,10 +1746,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729482</v>
+        <v>729734</v>
       </c>
       <c r="R12" t="n">
-        <v>7218068</v>
+        <v>7217951</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,10 +1926,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020680</v>
+        <v>127020644</v>
       </c>
       <c r="B14" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,34 +1937,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729872</v>
+        <v>729994</v>
       </c>
       <c r="R14" t="n">
-        <v>7217916</v>
+        <v>7217784</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020644</v>
+        <v>127020680</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,37 +2042,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729994</v>
+        <v>729872</v>
       </c>
       <c r="R15" t="n">
-        <v>7217784</v>
+        <v>7217916</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020702</v>
+        <v>127020654</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,34 +2245,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729956</v>
+        <v>729936</v>
       </c>
       <c r="R17" t="n">
-        <v>7217852</v>
+        <v>7217870</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,6 +2313,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020654</v>
+        <v>127020702</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,42 +2359,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729936</v>
+        <v>729956</v>
       </c>
       <c r="R18" t="n">
-        <v>7217870</v>
+        <v>7217852</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,11 +2419,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,10 +2651,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020713</v>
+        <v>127020671</v>
       </c>
       <c r="B21" t="n">
-        <v>80184</v>
+        <v>58558</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,21 +2662,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>208245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>729972</v>
+        <v>730037</v>
       </c>
       <c r="R21" t="n">
-        <v>7217816</v>
+        <v>7217806</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,6 +2730,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2752,10 +2753,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020671</v>
+        <v>127020713</v>
       </c>
       <c r="B22" t="n">
-        <v>58558</v>
+        <v>80184</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2763,21 +2764,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2787,10 +2788,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730037</v>
+        <v>729972</v>
       </c>
       <c r="R22" t="n">
-        <v>7217806</v>
+        <v>7217816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2831,7 +2832,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020679</v>
+        <v>127020639</v>
       </c>
       <c r="B27" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3308,21 +3308,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729853</v>
+        <v>729901</v>
       </c>
       <c r="R27" t="n">
-        <v>7217932</v>
+        <v>7217877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3376,7 +3376,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3500,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020639</v>
+        <v>127020679</v>
       </c>
       <c r="B29" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,21 +3510,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3535,10 +3534,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>729901</v>
+        <v>729853</v>
       </c>
       <c r="R29" t="n">
-        <v>7217877</v>
+        <v>7217932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3579,6 +3578,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4216,53 +4216,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020646</v>
+        <v>127020661</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731050</v>
+        <v>730715</v>
       </c>
       <c r="R36" t="n">
-        <v>7217071</v>
+        <v>7217263</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4295,11 +4287,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4330,45 +4317,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020661</v>
+        <v>127020646</v>
       </c>
       <c r="B37" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730715</v>
+        <v>731050</v>
       </c>
       <c r="R37" t="n">
-        <v>7217263</v>
+        <v>7217071</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4401,6 +4396,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4431,37 +4431,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020711</v>
+        <v>127020663</v>
       </c>
       <c r="B38" t="n">
-        <v>80184</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4469,10 +4474,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730711</v>
+        <v>730859</v>
       </c>
       <c r="R38" t="n">
-        <v>7217270</v>
+        <v>7217175</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4507,35 +4512,14 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran, hoppat över från sälg som stod mycket nära</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4556,42 +4540,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127020663</v>
+        <v>127020711</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>80184</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4599,10 +4578,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730859</v>
+        <v>730711</v>
       </c>
       <c r="R39" t="n">
-        <v>7217175</v>
+        <v>7217270</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4637,14 +4616,35 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gran, hoppat över från sälg som stod mycket nära</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4665,53 +4665,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020648</v>
+        <v>127020674</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730971</v>
+        <v>731014</v>
       </c>
       <c r="R40" t="n">
-        <v>7217152</v>
+        <v>7217177</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4744,11 +4736,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4779,45 +4766,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020674</v>
+        <v>127020648</v>
       </c>
       <c r="B41" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>731014</v>
+        <v>730971</v>
       </c>
       <c r="R41" t="n">
-        <v>7217177</v>
+        <v>7217152</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4850,6 +4845,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5711,32 +5711,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020710</v>
+        <v>127020632</v>
       </c>
       <c r="B50" t="n">
-        <v>80184</v>
+        <v>83012</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730874</v>
+        <v>730709</v>
       </c>
       <c r="R50" t="n">
-        <v>7217193</v>
+        <v>7217283</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5812,32 +5812,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020632</v>
+        <v>127020710</v>
       </c>
       <c r="B51" t="n">
-        <v>83012</v>
+        <v>80184</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730709</v>
+        <v>730874</v>
       </c>
       <c r="R51" t="n">
-        <v>7217283</v>
+        <v>7217193</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5913,32 +5913,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020695</v>
+        <v>127020669</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>97593</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730607</v>
+        <v>730976</v>
       </c>
       <c r="R52" t="n">
-        <v>7217333</v>
+        <v>7217157</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5984,11 +5984,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6019,32 +6014,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020669</v>
+        <v>127020695</v>
       </c>
       <c r="B53" t="n">
-        <v>97593</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6054,10 +6049,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730976</v>
+        <v>730607</v>
       </c>
       <c r="R53" t="n">
-        <v>7217157</v>
+        <v>7217333</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6090,6 +6085,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6327,10 +6327,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020667</v>
+        <v>127020698</v>
       </c>
       <c r="B56" t="n">
-        <v>91847</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6338,21 +6338,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730729</v>
+        <v>730776</v>
       </c>
       <c r="R56" t="n">
-        <v>7217314</v>
+        <v>7217232</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6428,10 +6428,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020698</v>
+        <v>127020667</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>91847</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6439,21 +6439,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730776</v>
+        <v>730729</v>
       </c>
       <c r="R57" t="n">
-        <v>7217232</v>
+        <v>7217314</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 30590-2025 artfynd.xlsx
+++ b/artfynd/A 30590-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127020670</v>
+        <v>127020672</v>
       </c>
       <c r="B2" t="n">
-        <v>97593</v>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729978</v>
+        <v>729986</v>
       </c>
       <c r="R2" t="n">
-        <v>7217767</v>
+        <v>7217775</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127020665</v>
+        <v>127020688</v>
       </c>
       <c r="B3" t="n">
-        <v>80053</v>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730028</v>
+        <v>729734</v>
       </c>
       <c r="R3" t="n">
-        <v>7217812</v>
+        <v>7217951</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020704</v>
+        <v>127020676</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729985</v>
+        <v>729643</v>
       </c>
       <c r="R4" t="n">
-        <v>7217794</v>
+        <v>7218002</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127020692</v>
+        <v>127020677</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729964</v>
+        <v>729603</v>
       </c>
       <c r="R5" t="n">
-        <v>7217823</v>
+        <v>7218099</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127020629</v>
+        <v>127020678</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,42 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729893</v>
+        <v>729589</v>
       </c>
       <c r="R6" t="n">
-        <v>7217893</v>
+        <v>7218061</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,11 +1151,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,53 +1181,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127020706</v>
+        <v>127020634</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729913</v>
+        <v>729735</v>
       </c>
       <c r="R7" t="n">
-        <v>7217887</v>
+        <v>7217963</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,11 +1252,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,45 +1282,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127020664</v>
+        <v>127020644</v>
       </c>
       <c r="B8" t="n">
-        <v>80053</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729960</v>
+        <v>729994</v>
       </c>
       <c r="R8" t="n">
-        <v>7217849</v>
+        <v>7217784</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,6 +1364,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1408,32 +1387,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127020662</v>
+        <v>127020692</v>
       </c>
       <c r="B9" t="n">
-        <v>80178</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729959</v>
+        <v>729964</v>
       </c>
       <c r="R9" t="n">
-        <v>7217826</v>
+        <v>7217823</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020688</v>
+        <v>127020693</v>
       </c>
       <c r="B10" t="n">
-        <v>91722</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,21 +1499,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1544,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729734</v>
+        <v>729531</v>
       </c>
       <c r="R10" t="n">
-        <v>7217951</v>
+        <v>7218052</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,14 +1589,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020693</v>
+        <v>127020702</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1645,10 +1624,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729531</v>
+        <v>729956</v>
       </c>
       <c r="R11" t="n">
-        <v>7218052</v>
+        <v>7217852</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,32 +1690,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020637</v>
+        <v>127020703</v>
       </c>
       <c r="B12" t="n">
-        <v>79663</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1746,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729482</v>
+        <v>729977</v>
       </c>
       <c r="R12" t="n">
-        <v>7218068</v>
+        <v>7217832</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,53 +1791,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020653</v>
+        <v>127020704</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729926</v>
+        <v>729985</v>
       </c>
       <c r="R13" t="n">
-        <v>7217876</v>
+        <v>7217794</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,11 +1862,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1926,32 +1892,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020680</v>
+        <v>127020705</v>
       </c>
       <c r="B14" t="n">
-        <v>78802</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1961,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729872</v>
+        <v>729987</v>
       </c>
       <c r="R14" t="n">
-        <v>7217916</v>
+        <v>7217772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,7 +1971,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2028,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020644</v>
+        <v>127020687</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,37 +2004,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729994</v>
+        <v>729998</v>
       </c>
       <c r="R15" t="n">
-        <v>7217784</v>
+        <v>7217750</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2110,7 +2072,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2133,32 +2094,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020712</v>
+        <v>127020635</v>
       </c>
       <c r="B16" t="n">
-        <v>80184</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729961</v>
+        <v>729516</v>
       </c>
       <c r="R16" t="n">
-        <v>7217852</v>
+        <v>7218058</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020702</v>
+        <v>127020637</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,21 +2206,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2269,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729956</v>
+        <v>729482</v>
       </c>
       <c r="R17" t="n">
-        <v>7217852</v>
+        <v>7218068</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020654</v>
+        <v>127020639</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,42 +2307,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729936</v>
+        <v>729901</v>
       </c>
       <c r="R18" t="n">
-        <v>7217870</v>
+        <v>7217877</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,11 +2367,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2449,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020676</v>
+        <v>127020640</v>
       </c>
       <c r="B19" t="n">
-        <v>91602</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,21 +2408,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2484,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>729643</v>
+        <v>729998</v>
       </c>
       <c r="R19" t="n">
-        <v>7218002</v>
+        <v>7217750</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,10 +2498,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020634</v>
+        <v>127020664</v>
       </c>
       <c r="B20" t="n">
-        <v>91513</v>
+        <v>80336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,21 +2509,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2585,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>729735</v>
+        <v>729960</v>
       </c>
       <c r="R20" t="n">
-        <v>7217963</v>
+        <v>7217849</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,10 +2599,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020713</v>
+        <v>127020665</v>
       </c>
       <c r="B21" t="n">
-        <v>80184</v>
+        <v>80336</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,21 +2610,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2686,10 +2634,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>729972</v>
+        <v>730028</v>
       </c>
       <c r="R21" t="n">
-        <v>7217816</v>
+        <v>7217812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2752,10 +2700,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020671</v>
+        <v>127020666</v>
       </c>
       <c r="B22" t="n">
-        <v>58558</v>
+        <v>80336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2763,21 +2711,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2787,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730037</v>
+        <v>730036</v>
       </c>
       <c r="R22" t="n">
-        <v>7217806</v>
+        <v>7217809</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2831,7 +2779,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2857,7 +2804,7 @@
         <v>127020675</v>
       </c>
       <c r="B23" t="n">
-        <v>80177</v>
+        <v>80460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,53 +2902,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020645</v>
+        <v>127020662</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729635</v>
+        <v>729959</v>
       </c>
       <c r="R24" t="n">
-        <v>7218021</v>
+        <v>7217826</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,11 +2973,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3069,53 +3003,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020631</v>
+        <v>127020712</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>80467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729898</v>
+        <v>729961</v>
       </c>
       <c r="R25" t="n">
-        <v>7217887</v>
+        <v>7217852</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,11 +3074,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,53 +3104,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020652</v>
+        <v>127020713</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>80467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729906</v>
+        <v>729972</v>
       </c>
       <c r="R26" t="n">
-        <v>7217885</v>
+        <v>7217816</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3262,11 +3175,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3297,10 +3205,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020679</v>
+        <v>127020629</v>
       </c>
       <c r="B27" t="n">
-        <v>78802</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3308,34 +3216,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729853</v>
+        <v>729893</v>
       </c>
       <c r="R27" t="n">
-        <v>7217932</v>
+        <v>7217893</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,13 +3286,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3399,10 +3319,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020705</v>
+        <v>127020631</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3410,34 +3330,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729987</v>
+        <v>729898</v>
       </c>
       <c r="R28" t="n">
-        <v>7217772</v>
+        <v>7217887</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3470,6 +3398,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3500,10 +3433,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020639</v>
+        <v>127020645</v>
       </c>
       <c r="B29" t="n">
-        <v>79663</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,34 +3444,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>729901</v>
+        <v>729635</v>
       </c>
       <c r="R29" t="n">
-        <v>7217877</v>
+        <v>7218021</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3571,6 +3512,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild 2</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3601,45 +3547,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020666</v>
+        <v>127020652</v>
       </c>
       <c r="B30" t="n">
-        <v>80053</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730036</v>
+        <v>729906</v>
       </c>
       <c r="R30" t="n">
-        <v>7217809</v>
+        <v>7217885</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,6 +3626,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3702,10 +3661,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020672</v>
+        <v>127020653</v>
       </c>
       <c r="B31" t="n">
-        <v>83004</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,34 +3672,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>729986</v>
+        <v>729926</v>
       </c>
       <c r="R31" t="n">
-        <v>7217775</v>
+        <v>7217876</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3775,13 +3742,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3804,10 +3775,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020658</v>
+        <v>127020654</v>
       </c>
       <c r="B32" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3815,21 +3786,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3837,7 +3808,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3847,10 +3818,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730021</v>
+        <v>729936</v>
       </c>
       <c r="R32" t="n">
-        <v>7217762</v>
+        <v>7217870</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3883,6 +3854,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3913,10 +3889,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020635</v>
+        <v>127020706</v>
       </c>
       <c r="B33" t="n">
-        <v>79663</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3924,34 +3900,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>729516</v>
+        <v>729913</v>
       </c>
       <c r="R33" t="n">
-        <v>7218058</v>
+        <v>7217887</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3984,6 +3968,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4014,10 +4003,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127020694</v>
+        <v>127020656</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4025,34 +4014,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730341</v>
+        <v>729998</v>
       </c>
       <c r="R34" t="n">
-        <v>7217488</v>
+        <v>7217749</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4085,6 +4086,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4115,10 +4121,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020700</v>
+        <v>127020657</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>58114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4126,34 +4132,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>731060</v>
+        <v>730017</v>
       </c>
       <c r="R35" t="n">
-        <v>7217069</v>
+        <v>7217786</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4216,10 +4230,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020646</v>
+        <v>127020658</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>58114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4227,21 +4241,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4249,7 +4263,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4259,10 +4273,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731050</v>
+        <v>730021</v>
       </c>
       <c r="R36" t="n">
-        <v>7217071</v>
+        <v>7217762</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4295,11 +4309,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4330,10 +4339,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020661</v>
+        <v>127020671</v>
       </c>
       <c r="B37" t="n">
-        <v>80178</v>
+        <v>58790</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4341,21 +4350,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>208245</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4365,10 +4374,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730715</v>
+        <v>730037</v>
       </c>
       <c r="R37" t="n">
-        <v>7217263</v>
+        <v>7217806</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4409,6 +4418,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4431,10 +4441,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020711</v>
+        <v>127020670</v>
       </c>
       <c r="B38" t="n">
-        <v>80184</v>
+        <v>97989</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4442,37 +4452,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730711</v>
+        <v>729978</v>
       </c>
       <c r="R38" t="n">
-        <v>7217270</v>
+        <v>7217767</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4507,35 +4514,14 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran, hoppat över från sälg som stod mycket nära</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4556,10 +4542,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127020663</v>
+        <v>127020679</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>79085</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4567,42 +4553,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730859</v>
+        <v>729853</v>
       </c>
       <c r="R39" t="n">
-        <v>7217175</v>
+        <v>7217932</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4643,6 +4621,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4644,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020648</v>
+        <v>127020680</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>79085</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4676,42 +4655,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730971</v>
+        <v>729872</v>
       </c>
       <c r="R40" t="n">
-        <v>7217152</v>
+        <v>7217916</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4746,17 +4717,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bild</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4779,32 +4746,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020674</v>
+        <v>127020694</v>
       </c>
       <c r="B41" t="n">
-        <v>80177</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4814,10 +4781,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>731014</v>
+        <v>730341</v>
       </c>
       <c r="R41" t="n">
-        <v>7217177</v>
+        <v>7217488</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4880,10 +4847,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020655</v>
+        <v>127020667</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>92208</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4891,21 +4858,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,10 +4882,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730778</v>
+        <v>730729</v>
       </c>
       <c r="R42" t="n">
-        <v>7217220</v>
+        <v>7217314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4951,11 +4918,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4989,7 +4951,7 @@
         <v>127020642</v>
       </c>
       <c r="B43" t="n">
-        <v>91549</v>
+        <v>91909</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5087,53 +5049,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127020647</v>
+        <v>127020689</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>731116</v>
+        <v>730685</v>
       </c>
       <c r="R44" t="n">
-        <v>7217118</v>
+        <v>7217290</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5166,11 +5120,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5201,14 +5150,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127020691</v>
+        <v>127020690</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5236,10 +5185,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730593</v>
+        <v>730712</v>
       </c>
       <c r="R45" t="n">
-        <v>7217363</v>
+        <v>7217261</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5272,11 +5221,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>6st långa bålar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5307,14 +5251,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127020699</v>
+        <v>127020691</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5342,10 +5286,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730843</v>
+        <v>730593</v>
       </c>
       <c r="R46" t="n">
-        <v>7217187</v>
+        <v>7217363</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5378,6 +5322,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>6st långa bålar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5408,14 +5357,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020701</v>
+        <v>127020695</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5443,10 +5392,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730947</v>
+        <v>730607</v>
       </c>
       <c r="R47" t="n">
-        <v>7217151</v>
+        <v>7217333</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5479,6 +5428,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5509,14 +5463,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020697</v>
+        <v>127020696</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5544,10 +5498,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730722</v>
+        <v>730712</v>
       </c>
       <c r="R48" t="n">
-        <v>7217249</v>
+        <v>7217282</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5580,6 +5534,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5610,14 +5569,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127020689</v>
+        <v>127020697</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5645,10 +5604,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730685</v>
+        <v>730722</v>
       </c>
       <c r="R49" t="n">
-        <v>7217290</v>
+        <v>7217249</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5711,27 +5670,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020710</v>
+        <v>127020698</v>
       </c>
       <c r="B50" t="n">
-        <v>80184</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5746,10 +5705,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730874</v>
+        <v>730776</v>
       </c>
       <c r="R50" t="n">
-        <v>7217193</v>
+        <v>7217232</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5812,32 +5771,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020632</v>
+        <v>127020699</v>
       </c>
       <c r="B51" t="n">
-        <v>83012</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5847,10 +5806,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730709</v>
+        <v>730843</v>
       </c>
       <c r="R51" t="n">
-        <v>7217283</v>
+        <v>7217187</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5913,14 +5872,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020695</v>
+        <v>127020700</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5948,10 +5907,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730607</v>
+        <v>731060</v>
       </c>
       <c r="R52" t="n">
-        <v>7217333</v>
+        <v>7217069</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5984,11 +5943,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6019,32 +5973,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020669</v>
+        <v>127020701</v>
       </c>
       <c r="B53" t="n">
-        <v>97593</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6054,10 +6008,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730976</v>
+        <v>730947</v>
       </c>
       <c r="R53" t="n">
-        <v>7217157</v>
+        <v>7217151</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6120,10 +6074,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020690</v>
+        <v>127020632</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>83307</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6131,21 +6085,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6155,10 +6109,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730712</v>
+        <v>730709</v>
       </c>
       <c r="R54" t="n">
-        <v>7217261</v>
+        <v>7217283</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6221,32 +6175,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020696</v>
+        <v>127020674</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>80460</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6256,10 +6210,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730712</v>
+        <v>731014</v>
       </c>
       <c r="R55" t="n">
-        <v>7217282</v>
+        <v>7217177</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6292,11 +6246,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6327,32 +6276,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020667</v>
+        <v>127020659</v>
       </c>
       <c r="B56" t="n">
-        <v>91847</v>
+        <v>80461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6362,10 +6311,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730729</v>
+        <v>730717</v>
       </c>
       <c r="R56" t="n">
-        <v>7217314</v>
+        <v>7217269</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6428,32 +6377,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020698</v>
+        <v>127020660</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>80461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6463,10 +6412,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730776</v>
+        <v>730716</v>
       </c>
       <c r="R57" t="n">
-        <v>7217232</v>
+        <v>7217261</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6529,10 +6478,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020708</v>
+        <v>127020661</v>
       </c>
       <c r="B58" t="n">
-        <v>80184</v>
+        <v>80461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6540,21 +6489,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6564,10 +6513,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730721</v>
+        <v>730715</v>
       </c>
       <c r="R58" t="n">
-        <v>7217258</v>
+        <v>7217263</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6630,10 +6579,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127020660</v>
+        <v>127020708</v>
       </c>
       <c r="B59" t="n">
-        <v>80178</v>
+        <v>80467</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6641,21 +6590,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6665,10 +6614,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730716</v>
+        <v>730721</v>
       </c>
       <c r="R59" t="n">
-        <v>7217261</v>
+        <v>7217258</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6731,10 +6680,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020659</v>
+        <v>127020710</v>
       </c>
       <c r="B60" t="n">
-        <v>80178</v>
+        <v>80467</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6742,21 +6691,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6766,10 +6715,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730717</v>
+        <v>730874</v>
       </c>
       <c r="R60" t="n">
-        <v>7217269</v>
+        <v>7217193</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6832,10 +6781,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020668</v>
+        <v>127020711</v>
       </c>
       <c r="B61" t="n">
-        <v>97593</v>
+        <v>80467</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6843,34 +6792,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skansberget, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>731110</v>
+        <v>730711</v>
       </c>
       <c r="R61" t="n">
-        <v>7217020</v>
+        <v>7217270</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6905,14 +6857,35 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gran, hoppat över från sälg som stod mycket nära</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6926,6 +6899,879 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127020663</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skansberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>730859</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7217175</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127020646</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skansberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>731050</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7217071</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127020647</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skansberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>731116</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7217118</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127020648</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skansberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>730971</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7217152</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack bild</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127020651</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skansberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>730774</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7217314</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127020655</v>
+      </c>
+      <c r="B67" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skansberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>730778</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7217220</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127020668</v>
+      </c>
+      <c r="B68" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skansberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>731110</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7217020</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127020669</v>
+      </c>
+      <c r="B69" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skansberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>730976</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7217157</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
